--- a/data/revisoes/handebol/atualizacao_humor_2026-10/tabela_extracao_completa_humor_handebol.xlsx
+++ b/data/revisoes/handebol/atualizacao_humor_2026-10/tabela_extracao_completa_humor_handebol.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Método e legenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extração completa'!$A$1:$AE$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extração completa'!$A$1:$AE$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3685,175 +3685,20 @@
     <row r="21" ht="210" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>U107</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>(NUGRAHA; WIBOWO; FIRMANSYAH, 2020)</t>
+          <t>(BATALLA-GAVALDA et al., 2021)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>NUGRAHA, E.; WIBOWO, R.; FIRMANSYAH, H. Mood states and game performance in invasion game activities: a correlation study among elementary school students. *In*: INTERNATIONAL CONFERENCE ON SPORT SCIENCE, HEALTH, AND PHYSICAL EDUCATION, 4., 2019, Bandung. Proceedings [...]. Paris: Atlantis Press, 2020. p. 95-98. DOI: https://doi.org/10.2991/ahsr.k.200214.027.</t>
+          <t>BATALLA-GAVALDA, A. et al. Variations in the Mood States during the Different Phases of COVID-19’s Lockdown in Young Athletes. International Journal of Environmental Research and Public Health, v. 18, n. 17, e9326, 2021. DOI: https://doi.org/10.3390/ijerph18179326.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>• NUGRAHA, Eka
-• WIBOWO, Ricky
-• FIRMANSYAH, Helmy</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Mood States and Game Performance in Invasion Game Activities: A Correlation Study Among Elementary School Students</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Proceedings of the 4th International Conference on Sport Science, Health, and Physical Education (ICSSHPE 2019)</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica (anais)</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.2991/ahsr.k.200214.027</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Children play games for the same reason. They play because playing is fun. Interest to games may have meaningful psychological benefits for children. The purpose of this study was to examine the association between short-term psychological effects, especially moods states, and games performance in invasion game activities setting at elementary students. Correlational approach was used to analyse the results of this study. Third grade elementary school students were enrolled in this study. Forty elementary students were assigned to invasion games in 8 minute game, which was divided into two minute halves. The game taught used invasion games was handball, which fields size and rules were modified. Pleasant and unpleasant moods using Brief Mood Introspection Scale (BMIS) were assessed before experimental conditions. BMIS with 8 sub-scales pleasant mood states (active, calm, caring, content, happy, lively, loving, and peppy) and unpleasant mood states (drowsy, fed up, gloomy, grouchy, jittery, nervous, sad, and tired) are rated on a 4-point Likert scale ranging from 1 (definitely do not feel) to 4 (definitely feel). It was found that pleasant moods states correlated with games performance and games involvement of the student in games activities. This study suggests physical educators to setting motivated climate to increase moods states in order to engage children in physical activities.</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>Examinar a associação entre efeitos psicológicos de curto prazo, em especial os estados de humor, e o desempenho de jogo em atividades de jogo de invasão (handebol modificado) em escolares do ensino fundamental.</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>Observacional correlacional.</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>Transversal, com BMIS aplicada uma vez antes do aquecimento e de um jogo de invasão 4 contra 4 de 8 min (duas rodadas de 4 min) e correlação de Pearson entre humor e desempenho e envolvimento.</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>Escolares do 3º ano do ensino fundamental, de ambos os sexos, em jogo de invasão baseado no handebol (regras e quadra modificadas, sem goleiro) em aula de educação física; não são atletas; Indonésia.</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>40 escolares (21 meninas e 19 meninos), 9,1 ± 0,54 anos; altura 1,25 ± 0,3; massa 27,4 ± 0,3; perdas não relatadas.</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>Indonésia</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>• Humor agradável, humor desagradável e escore total agradável-desagradável: Brief Mood Introspection Scale (BMIS) adaptada de 16 itens</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>• Brief Mood Introspection Scale (BMIS), adaptada, 16 itens (8 agradáveis e 8 desagradáveis), escala Likert de 4 pontos, itens desagradáveis invertidos; confiabilidade não relatada
-• Game Performance Assessment Instrument (GPAI: tomada de decisão, execução e suporte) e índice de envolvimento no jogo, por vídeo</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t>BMIS preenchido antes do aquecimento e do jogo, com a pergunta "What do you feel right now?" e orientação dos pesquisadores; em seguida, aquecimento padronizado de 10 min e jogo de invasão de 8 min em duas rodadas de 4 min (o resumo menciona metades de dois minutos).</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>Humor agradável 2,9487 ± 0,66416; desagradável (invertido) 2,7830 ± 0,76264; total 2,8655 ± 0,66539. Humor agradável correlacionou-se com desempenho de jogo (r = 0,336; p = 0,034) e com envolvimento (r = 0,587; p &lt; 0,001); humor desagradável invertido correlacionou-se com envolvimento (r = 0,508; p = 0,001), mas não com desempenho (r = 0,170; p = 0,294); escore total correlacionou-se com envolvimento (r = 0,585; p &lt; 0,001), mas não com desempenho (r = 0,266; p = 0,097). Envolvimento e desempenho correlacionaram-se entre si (r = 0,353; p = 0,026).</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t>Efeito ou associação</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
-        <is>
-          <t>texto completo</t>
-        </is>
-      </c>
-      <c r="AC21" s="3" t="inlineStr">
-        <is>
-          <t>• Os autores sugerem investigar fatores que melhorem o humor das crianças no início e durante a aula.
-• Delineamento transversal sem controle de sexo e de habilidade prévia.
-• Confiabilidade da BMIS adaptada não relatada e erros de descrição da pontuação, da duração do jogo e dos DP antropométricos.
-• Contexto escolar com handebol modificado, sem extensão a atletas de handebol.</t>
-        </is>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
-        <is>
-          <t>O estudo mostra que o humor agradável antes de um jogo de handebol modificado se correlaciona de forma moderada com o envolvimento e de forma fraca com o desempenho de escolares de 9 anos. A robustez é limitada pelo delineamento transversal, pela amostra pequena e por imprecisões de relato. A contribuição para o tema é estender a relação entre humor e desempenho ao ensino do handebol na infância.</t>
-        </is>
-      </c>
-      <c r="AE21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="210" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>(BATALLA-GAVALDA et al., 2021)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>BATALLA-GAVALDA, A. et al. Variations in the Mood States during the Different Phases of COVID-19’s Lockdown in Young Athletes. International Journal of Environmental Research and Public Health, v. 18, n. 17, e9326, 2021. DOI: https://doi.org/10.3390/ijerph18179326.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>• BATALLA-GAVALDA, Abraham
 • CECILIA-GALLEGO, Pau
@@ -3861,123 +3706,123 @@
 • BELTRAN-GARRIDO, Jose Vicente</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Variations in the Mood States during the Different Phases of COVID-19’s Lockdown in Young Athletes</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>International Journal of Environmental Research and Public Health</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>1660-4601</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/ijerph18179326</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>The pandemic caused by SARS-CoV-2 led to a situation of home lockdown. Competitions, training, and sports activities were canceled for much of this period. This situation could have affected the physical and mental health and the mood states of young athletes. The aim of the study was to evaluate the variations in the mood states of young athletes of a highly competitive level during the different phases of lockdown in. The mood states of 45 Spanish youth athletes confined during the 10-week lockdown due to the COVID-19 pandemic -19 were assessed, using the Spanish-translated version of the POMS questionnaire, at the start of the home lockdown and at the start and at the end of the partial lockdown. The Total Mood Disturbance scores at week 10 were lower than those obtained in week 1 (p Bonferroni = 0.031). The depression scores at week 6 (p Bonferroni = 0.048) and at week 10 (p Bonferroni &lt; 0.001) were lower than those obtained in week 1. The confusion scores at week 10 were lower than those obtained in week 1 (p Bonferroni = 0.002). These variations differed between team and individual sports. In conclusion, the lockdown produced changes in the young athletes’ mood states that should be considered when trying to optimize their physical and mental performance.</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Avaliar as variações dos estados de humor de jovens atletas de nível competitivo alto durante as diferentes fases do confinamento por COVID-19 na Espanha, sob a hipótese de que o confinamento afetaria de forma negativa esses estados.</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>Observacional.</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>Longitudinal, com três medidas repetidas (semanas 1, 6 e 10 do confinamento de 10 semanas, de março a maio de 2020): início do confinamento domiciliar, início do confinamento parcial e fim do confinamento parcial; comparações no tempo (amostra total) e entre modalidades e sexos em cada momento.</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>Jovens atletas de nível competitivo alto de um centro de tecnificação esportiva (Centre de Tecnificació Terres de l'Ebre, Tarragona) de atletismo, handebol e natação; no handebol, apenas atletas do sexo feminino; Espanha.</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>80 atletas recrutados por conveniência; 45 analisados por completarem as três medidas (perda de 35). Handebol: 16 atletas do sexo feminino, 15,94 ± 0,68 anos. Atletismo: 18 (9 do sexo masculino e 9 do feminino), 16,89 ± 2,05 anos. Natação: 11 (5 do sexo masculino e 6 do feminino), 15,27 ± 1,10 anos.</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>Espanha</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor (tensão-ansiedade, depressão-desânimo, raiva-hostilidade, vigor-atividade, fadiga-inércia, confusão-desorientação e PTH): POMS, versão espanhola de 58 itens</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t>• POMS, versão espanhola de 58 itens, escala Likert de 0 (nada) a 4 (extremamente), seis subescalas; PTH = soma das subescalas negativas menos vigor, mais constante de 100; confiabilidade não relatada</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
         <is>
           <t>POMS aplicado na semana 1 (início do confinamento domiciliar), na semana 6 (fim do confinamento domiciliar e início do confinamento parcial) e na semana 10 (fim do confinamento parcial). Forma de aplicação e período de referência n.r.</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>Handebol, semanas 1, 6 e 10: PTH 136,94 ± 26,62; 139,81 ± 32,33; 135,54 ± 33,26. Tensão 11,38 ± 5,51; 11,80 ± 6,49; 10,08 ± 7,03. Depressão 10,56 ± 8,16; 11,60 ± 8,76; 10,85 ± 8,51. Raiva 12,00 ± 8,15; 14,53 ± 9,32; 12,69 ± 9,99. Vigor 13,81 ± 5,15; 12,87 ± 5,08; 13,39 ± 3,53. Fadiga 6,56 ± 4,63; 7,20 ± 4,75; 6,31 ± 5,60. Confusão 10,25 ± 5,03; 10,20 ± 4,25; 9,00 ± 5,34. PTH do handebol maior que a do atletismo nas três semanas (pBonferroni = 0,024; 0,016; 0,013); depressão e confusão maiores que no atletismo nas semanas 6 e 10 (depressão pBonferroni = 0,012; confusão pBonferroni = 0,001); na semana 6, raiva maior que no atletismo (pBonferroni = 0,005) e na natação (pBonferroni = 0,030) e tensão maior que na natação (pBonferroni = 0,020); vigor e fadiga sem diferença entre modalidades. Amostra total: PTH de 126,55 ± 27,64 (semana 1) para 117,65 ± 29,26 (semana 10; pBonferroni = 0,031); depressão e confusão diminuíram; sem efeito do sexo. O efeito do tempo não foi testado dentro do handebol.</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="n">
+      <c r="AA21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
+      <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC22" s="2" t="inlineStr">
+      <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>• Ausência de medida do humor antes da pandemia na mesma população, declarada pelos autores.
 • Falta de variáveis como saúde mental e quantidade e qualidade do sono, conforme os autores.
@@ -3985,30 +3830,30 @@
 • Efeito do tempo não testado dentro do handebol e perda de 44% da amostra recrutada.</t>
         </is>
       </c>
-      <c r="AD22" s="2" t="inlineStr">
+      <c r="AD21" s="3" t="inlineStr">
         <is>
           <t>O estudo acompanha o humor de jovens atletas em três fases do confinamento e mostra queda da PTH, da depressão e da confusão na amostra total, enquanto as jogadoras de handebol mantêm PTH estável e mais alta que a do atletismo. A robustez é moderada a baixa, pela perda amostral, pela confusão entre modalidade e sexo e por divergências entre texto e tabelas. A contribuição para o tema é sugerir maior vulnerabilidade do humor de jovens handebolistas à suspensão do treino coletivo, hipótese que exige confirmação com grupos equilibrados por sexo.</t>
         </is>
       </c>
-      <c r="AE22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="210" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="AE21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="210" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>H23</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>(GARCÍA-HERRERO et al., 2022)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>GARCÍA-HERRERO, J. A. et al. Analysis of the Relationship between Satisfaction with the Coach and the Effect of Comparative Social Feedback in Elite Female Handball Players. International Journal of Environmental Research and Public Health, v. 19, n. 13, e7680, 2022. DOI: https://doi.org/10.3390/ijerph19137680.</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>• GARCÍA-HERRERO, Juan Antonio
 • SOTO-GARCÍA, Diego
@@ -4017,85 +3862,85 @@
 • DELGADO-FLOODY, Pedro</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Analysis of the Relationship between Satisfaction with the Coach and the Effect of Comparative Social Feedback in Elite Female Handball Players</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F22" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>International Journal of Environmental Research and Public Health</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1660-4601</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/ijerph19137680</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>This research aims at studying the effect of comparative feedback on psychological variables (competence valuation, perceived competence, autonomous motivation, amotivation, subjective well-being) and performance (throwing speed and accuracy). A total of 73 handball players from the highest Spanish handball (Iberdrola League) category participated in this study. After previously rating satisfaction with their head coach, they were indiscriminately assigned to one of three different experimental conditions measuring feedback, positive, negative, and none. There were significant differences in competence valuation, perceived competence, autonomous motivation, and throwing speed in the three feedback groups, more concretely, low satisfaction with the head coach. Positive effects were found when there was low satisfaction with the coach and positive feedback on the competence valuation, autonomous motivation, and throwing speed compared to negative or no feedback. These results have important implications for optimizing coaches’ behaviors in relation to athlete well-being and performance. [idioma: inglês; texto literal do XML PMC9266220]</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Estudar o efeito do feedback comparativo sobre variáveis psicológicas (valorização da competência, competência percebida, motivação autônoma, amotivação e bem-estar subjetivo) e sobre o desempenho (velocidade e precisão do arremesso), conforme a satisfação com o treinador.</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>Experimental</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>Fatorial 3 × 2 × 2: feedback comparativo (positivo, negativo, ausente; alocação aleatória) × satisfação com o treinador (baixa ou alta) × tempo (antes e depois de uma tarefa única de 21 arremessos), com feedback pré-estabelecido a cada 3 arremessos dado pelos próprios treinadores; sem cegamento.</t>
         </is>
       </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Jogadoras de linha de elite da Liga Iberdrola (primeira divisão espanhola), sexo feminino, maiores de idade, Espanha.</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>73 jogadoras participantes, 70 com dados completos; 23,13 ± 4,05 anos; feedback positivo n = 26, negativo n = 22, ausente n = 22 (baixa satisfação: 11, 6 e 7; alta satisfação: 15, 16 e 15); goleiras e lesionadas excluídas.</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>Espanha</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>• Afeto positivo e afeto negativo (bem-estar subjetivo): PANAS, versão espanhola (20 itens)
 • Satisfação com o treinador: APCCS II-HST reduzida (3 itens)
@@ -4104,7 +3949,7 @@
 • Motivação autônoma e amotivação: subescalas da versão espanhola da EMS</t>
         </is>
       </c>
-      <c r="V23" s="3" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>• PANAS, versão espanhola, 20 itens, escala de 1 a 5; afeto positivo α = 0,87 e 0,89 (CCI = 0,69); afeto negativo α = 0,82 e 0,86 (CCI = 0,63)
 • APCCS II-HST, versão espanhola reduzida, 3 itens, escala de 1 a 5; α = 0,67
@@ -4114,65 +3959,65 @@
 • Tarefa de 21 arremessos com medida da velocidade da bola por radar e da precisão</t>
         </is>
       </c>
-      <c r="W23" s="3" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Satisfação com o treinador avaliada no primeiro dia; PANAS e demais escalas respondidos em sala privada imediatamente antes e depois da tarefa de arremesso, após aquecimento padronizado de 12 min e três arremessos máximos.</t>
         </is>
       </c>
-      <c r="X23" s="3" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>feedback comparativo pré-estabelecido (positivo, negativo ou ausente) durante 21 arremessos, analisado segundo satisfação baixa ou alta com o treinador</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>Afeto positivo e afeto negativo não se alteraram: nenhum efeito principal ou interação foi significativo (afeto positivo: feedback × tempo F = 1,45; interação tripla F = 0,32; afeto negativo: feedback × tempo F = 0,04; interação tripla F = 0,17). Medianas do afeto positivo antes e depois na baixa satisfação: sem feedback 3,70 e 3,30; positivo 3,90 e 4,10; negativo 3,75 e 3,60. Nas demais variáveis, a competência percebida aumentou após feedback positivo (delta = 0,26) e caiu após feedback negativo (delta = 0,28; interação F = 4,08; p &lt; 0,05); a valorização da competência foi maior com feedback positivo na baixa satisfação (F = 5,65; p &lt; 0,01); a motivação autônoma aumentou só na baixa satisfação com feedback positivo (interação tripla F = 3,33; p &lt; 0,05); a amotivação apresentou efeitos de satisfação (F = 5,54) e de feedback (F = 7,46); a velocidade caiu no grupo de baixa satisfação (F = 5,10; p &lt; 0,05).</t>
         </is>
       </c>
-      <c r="Z23" s="3" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>Sem efeito</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="n">
+      <c r="AA22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC23" s="3" t="inlineStr">
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>• Os autores reconhecem tarefa específica única, efeito estudado a curto prazo, fora de competição real, e amostra apenas feminina.
 • Subgrupos de baixa satisfação muito pequenos (6 a 11), com baixo poder para interações de três fatores.
 • Critério de divisão entre baixa e alta satisfação não descrito e descritivos do PANAS sem medida de dispersão.</t>
         </is>
       </c>
-      <c r="AD23" s="3" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>O experimento indica que o feedback comparativo, dado pelos próprios treinadores, não altera o afeto positivo nem o negativo de jogadoras de elite, embora modifique a competência percebida, a motivação e a velocidade conforme a satisfação com o treinador. A robustez é moderada, com alocação aleatória e instrumentos confiáveis, mas limitada pelos subgrupos pequenos. A contribuição para o tema consiste em mostrar estabilidade do afeto diante do feedback em atletas de elite, em contraste com o estudo anterior do mesmo grupo com feedback de pesquisador externo.</t>
         </is>
       </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="210" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="210" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>H24</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>(GHAZEL et al., 2022)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>GHAZEL, N. et al. The effect of music on short-term exercise performance during the different menstrual cycle phases in female handball players. Research in Sports Medicine, v. 30, n. 1, p. 50-60, 2022. DOI: https://doi.org/10.1080/15438627.2020.1860045.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>• GHAZEL, Nourhen
 • SOUISSI, Amine
@@ -4181,156 +4026,156 @@
 • SOUISSI, Nizar</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>The effect of music on short-term exercise performance during the different menstrual cycle phases in female handball players</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Research in Sports Medicine</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>1543-8627, 1543-8635</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/15438627.2020.1860045</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>The present study aimed to evaluate the effect of music on short-term exercise performance during the different menstrual cycle phases (MCP). In different MCP (i.e. menstrual phase (MP), luteal phase (LP), follicular phase (FP)) and in a randomized order, fourteen female handball players aged between 21-24 years performed during music (fast-tempo, 140 bpm) and no-music conditions the following tests: squat jump (SJ) test, countermovement jump (CMJ), agility T-test (TT), and repeated sprint ability (RSA). The profile of mood states (POMS) questionnaire was completed in the different MCP. The rating of perceived exertion was recorded at the end of TT and RSA. MCP does not affect the SJ, CMJ, TT and RSA performance. However, anxiety, anger, and confusion were higher in MP compared to LP and FP. Music enhances the SJ performance during the different MCP. However, the music improved the SJ performance (the first test) only following warm-up in all MCP. In conclusion, listening to music during warm-up could be beneficial for short-term exercise performance in all MCP, but the potential effect of the music on physical performance vanishes over time. [idioma: inglês; texto literal do PubMed/Europe PMC, PMID 33291988]</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>Avaliar o efeito da música sobre o desempenho em exercícios de curta duração nas diferentes fases do ciclo menstrual.</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>Experimental</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>Medidas repetidas com dois fatores intrassujeito: fase do ciclo menstrual (menstrual, lútea e folicular) e condição (música rápida de 140 bpm ou sem música), em ordem aleatória; POMS aplicado em cada fase do ciclo.</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>Jogadoras de handebol, sexo feminino, 21 a 24 anos, Tunísia (afiliação dos autores); nível competitivo n.r. no resumo.</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>n = 14 mulheres de 21 a 24 anos; média e DP da idade e perdas n.r. no resumo.</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="T23" s="3" t="inlineStr">
         <is>
           <t>Tunísia</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="U23" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor, com resultados relatados para ansiedade, raiva e confusão (POMS)
 • Percepção subjetiva do esforço (registrada ao final do teste T e dos sprints repetidos; instrumento n.r. no resumo)</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V23" s="3" t="inlineStr">
         <is>
           <t>• Profile of Mood States (POMS); versão e número de itens n.r. no resumo
 • Squat jump, salto com contramovimento, teste T de agilidade e teste de capacidade de sprints repetidos
 • Música de ritmo rápido (140 bpm) como condição experimental</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W23" s="3" t="inlineStr">
         <is>
           <t>POMS preenchido em cada fase do ciclo menstrual (menstrual, lútea e folicular); não se sabe, pelo resumo, se foi aplicado nas duas condições (com e sem música) nem em que momento da sessão. PSE registrada ao final do teste T e dos sprints repetidos.</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="X23" s="3" t="inlineStr">
         <is>
           <t>música de ritmo rápido (140 bpm) contra ausência de música, em ordem aleatória, em cada fase do ciclo menstrual</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>Ansiedade, raiva e confusão foram maiores na fase menstrual que nas fases lútea e folicular (valores numéricos e estatísticas n.r. no resumo). A fase do ciclo não afetou squat jump, salto com contramovimento, teste T nem sprints repetidos. A música melhorou o squat jump em todas as fases, apenas no primeiro teste após o aquecimento, e o efeito desapareceu ao longo do tempo.</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="n">
+      <c r="AA23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB23" s="3" t="inlineStr">
         <is>
           <t>resumo</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AC23" s="3" t="inlineStr">
         <is>
           <t>• Somente o resumo foi acessível, sem médias, DP, testes ou resultados das demais dimensões do POMS.
 • Não se sabe se o humor foi analisado separadamente por condição de música nem como as fases do ciclo foram verificadas.
 • O resumo não interpreta o achado de humor, e a relação entre humor e desempenho não é explorada.</t>
         </is>
       </c>
-      <c r="AD24" s="2" t="inlineStr">
+      <c r="AD23" s="3" t="inlineStr">
         <is>
           <t>O estudo indica maior ansiedade, raiva e confusão na fase menstrual em jogadoras de handebol, sem efeito da fase sobre o desempenho de curta duração, e benefício apenas transitório da música no aquecimento. A robustez é incerta, pois apenas o resumo foi lido e a amostra é pequena. A contribuição para o tema reside em reforçar o ciclo menstrual como fonte de variação do humor em atletas de handebol.</t>
         </is>
       </c>
-      <c r="AE24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="210" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="AE23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="210" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>H25</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>(SAHLI et al., 2022)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>SAHLI, F. et al. The Effects of Combined Verbal Encouragement and Technical Instruction on Technical Skills and Psychophysiological Responses During Small-Sided Handball Games Exercise in Physical Education. Frontiers in Psychology, v. 13, e902088, 2022. DOI: https://doi.org/10.3389/fpsyg.2022.902088.</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>• SAHLI, Feten
 • HAMMAMI, Raouf
@@ -4341,156 +4186,156 @@
 • VAN DEN TILLAAR, Roland</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>The Effects of Combined Verbal Encouragement and Technical Instruction on Technical Skills and Psychophysiological Responses During Small-Sided Handball Games Exercise in Physical Education</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Frontiers in Psychology</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>1664-1078</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fpsyg.2022.902088</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>To examine the effects of combined positive verbal encouragement and general technical guidelines on technical and psychophysiological parameters in pupils during a small-sided handball passing game. Twenty secondary school pupils (age, 16 ± 1 years; body mass, 55.3 ± 6.6 kg; body height, 1.77 ± 0.13 m; BMI, 22.6 ± 2.2 kg m −1) performed small-sided games (2 × 10 min) with three conditions: small-sided game (1) with combined verbal encouragement and technical instruction; (2) with technical instruction; (3) without any instruction (control) in which the passes for each pupil in each set was measured together with the rate of perceived exertion (RPE) and feeling mood after the first and second set. Results: A two-way analysis of variance demonstrated that the combined condition resulted in more passes compared to the technical instruction and control conditions, while the number of passes increased in set 2 for all conditions. RPE and the feeling mood were also differently between the conditions. Combined verbal encouragement and technical instruction during handball exercise were more beneficial for optimal passing numbers, positive mood with less perception of physical effort compared to only technical instruction and a control condition. The results evidenced positive acute effects of combined verbal encouragement and technical instruction during handball, indicating the usefulness of these training methods for optimal passing numbers, positive mood with less perception of physical effort in physical education pupils. Future studies should evaluate the applicability combined verbal encouragement and technical skills in the training of other conditioning capacities and the individual responsiveness of players toward verbal encouragement tasks. [idioma: inglês; texto literal do XML PMC]</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Examinar os efeitos da combinação de encorajamento verbal positivo e instruções técnicas gerais sobre parâmetros técnicos e psicofisiológicos de escolares durante um jogo reduzido de passes de handebol.</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Experimental</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>Intrassujeito do tipo cruzado (os autores o chamam de transversal intrassujeito): após familiarização, três sessões em ordem aleatória (encorajamento verbal com instrução técnica, apenas instrução técnica e controle), cada uma com jogo reduzido de passes 5 contra 5 em duas séries de 10 min e 2 min de recuperação, separadas por pelo menos 48 h; Feeling Scale no intervalo e após o jogo.</t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Escolares do ensino secundário, sexo masculino, 16 anos em média, ativos na educação física e sem experiência competitiva no handebol, Kef, Tunísia.</t>
         </is>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>n = 20 alunos do sexo masculino; idade 16 ± 1 anos; massa corporal 55,3 ± 6,6 kg; estatura 1,77 ± 0,13 m; IMC 22,6 ± 2,2; perdas não relatadas.</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>Tunísia</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>• Valência afetiva (humor percebido): Feeling Scale (Hardy e Rejeski, 1989), item único de -5 a +5
 • Percepção subjetiva do esforço: escala CR10 de Borg</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>• Feeling Scale (Hardy e Rejeski, 1989), item único How do you feel right now?, escala de -5 a +5; confiabilidade n.r.
 • Escala CR10 de Borg (PSE)
 • Contagem do número de passes por aluno em cada série</t>
         </is>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>A Feeling Scale foi aplicada duas vezes em cada sessão: no intervalo de recuperação entre as duas séries de 10 min e após o término do jogo (pós-teste). A PSE (Borg CR10) foi registrada após cada série.</t>
         </is>
       </c>
-      <c r="X25" s="3" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>três condições em ordem aleatória: encorajamento verbal combinado com instrução técnica, só instrução técnica e controle sem instrução</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>Para PSE e Feeling Scale, as estatísticas foram relatadas em conjunto: efeito da condição (F ≥ 9,2; p &lt; 0,001; ηp² = 0,32), do tempo (F ≥ 16,2; p &lt; 0,001; ηp² ≥ 0,46) e interação (F ≥ 4,5; p ≤ 0,018; ηp² ≥ 0,19). A Feeling Scale foi maior na condição combinada que no controle durante a recuperação; nas condições de instrução técnica e controle, o escore caiu da recuperação para o pós-teste, ao passo que na condição combinada não houve mudança significativa (médias apenas em figura). Passes: efeito da condição (F = 48,6; p &lt; 0,001; ηp² = 0,72), do tempo (F = 57,1; p &lt; 0,001; ηp² = 0,75) e interação (F = 10,6; p &lt; 0,001; ηp² = 0,36), com mais passes na condição combinada na primeira série. A PSE após a primeira série foi menor na condição combinada.</t>
         </is>
       </c>
-      <c r="Z25" s="3" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA25" s="3" t="n">
+      <c r="AA24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AB25" s="3" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC25" s="3" t="inlineStr">
+      <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>• Os autores reconhecem amostra pequena e restrita a jovens, ausência de avaliação autêntica do jogo e de medidas fisiológicas (lactato, frequência cardíaca, GPS).
 • Os autores apontam a inexperiência dos participantes no handebol, o que limita a transferência para equipes da modalidade, e a ausência de questionários que expliquem o humor mais positivo.
 • Estatísticas da Feeling Scale relatadas em bloco com a PSE e médias apenas em figura, o que impede isolar o efeito sobre o afeto.</t>
         </is>
       </c>
-      <c r="AD25" s="3" t="inlineStr">
+      <c r="AD24" s="2" t="inlineStr">
         <is>
           <t>O estudo cruzado mostra que a combinação de encorajamento verbal e instrução técnica mantém o afeto positivo e aumenta o número de passes durante jogo reduzido de handebol em escolares, ao passo que nas outras condições o afeto cai ao final. A robustez é moderada a baixa, pela amostra pequena, pelo relato estatístico conjunto e pela ausência de descrição da aleatorização. A contribuição para o tema reside em indicar o comportamento verbal do professor como modulador do estado afetivo no ensino do handebol, embora com participantes que não são atletas.</t>
         </is>
       </c>
-      <c r="AE25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26" ht="210" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="AE24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="210" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>O1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>(ESSID et al., 2022)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>ESSID, S. et al. Time-of-day effects in physical performances and psychological responses in young elite male handball players. Biological Rhythm Research, v. 53, n. 8, p. 1261-1272, 2022. DOI: https://doi.org/10.1080/09291016.2021.1922212.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>• ESSID, Sana
 • CHERIF, Moncef
@@ -4498,85 +4343,85 @@
 • SOUISSI, Nizar</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Time-of-day effects in physical performances and psychological responses in young elite male handball players</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Biological Rhythm Research</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>0929-1016, 1744-4179</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>não classificado na área</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>não classificado na área</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1080/09291016.2021.1922212</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>The present study examined the effect of time-of-day in psychological responses and short-term maximal performances in elite male handball players. Eighteen male handball players performed, in a counterbalanced order and at three time-of-day (i.e., in the morning at 10:00 h, in the afternoon at 14:00 h and in the evening at 18:00 h) the Repeated Sprint Ability (RSA) and the Ball-Throwing Velocity (BTV) test. Profile of mood states (POMS), simple (SRT) and choice (CRT) reaction times, and Stroop test to evaluate selective attention (SA) and Hooper questionnaires were assessed before the physical tests. Oral temperature (OT) was measured in the beginning of each testing session. The results revealed, for the POMS questionnaire, that the negative mood-states (anxiety, anger, confusion, depression, and fatigue) were higher in the morning while positive mood-state (vigor) was higher in the evening. Also, SRT, CRT and SA were better in the evening. For physical tests, BTV and performance during the RSA test were also better in the evening. OT was higher in the evening than in the morning and the afternoon. The findings suggest that, in elite handball players, cognitive and short-term maximal physical performances were better increased during the day from the morning to the evening.</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>Examinar o efeito do horário do dia sobre as respostas psicológicas e os desempenhos máximos de curta duração em jogadores de handebol de elite do sexo masculino.</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>Experimental (comparação intrassujeito entre horários).</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>Cruzado, com três condições (10h, 14h e 18h) em ordem contrabalançada; em cada sessão, temperatura oral no início, POMS, tempos de reação, Stroop e questionário de Hooper antes dos testes físicos (RSA e BTV).</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>Jogadores de handebol jovens de elite do sexo masculino; afiliações dos autores na Tunísia; idade não informada no resumo.</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t>18 jogadores do sexo masculino; idade, critérios de inclusão e perdas não informados no resumo.</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="T25" s="3" t="inlineStr">
         <is>
           <t>Tunísia</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="U25" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor (ansiedade, raiva, confusão, depressão, fadiga e vigor): POMS (versão não informada no resumo)
 • Indicadores de bem-estar percebido: questionário de Hooper
@@ -4584,7 +4429,7 @@
 • Atenção seletiva: teste de Stroop</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V25" s="3" t="inlineStr">
         <is>
           <t>• Profile of Mood States (POMS); versão, número de itens e confiabilidade não informados no resumo
 • Questionário de Hooper
@@ -4594,35 +4439,35 @@
 • Temperatura oral</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t>POMS aplicado antes dos testes físicos em cada um dos três horários (10h, 14h e 18h).</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t>não se aplica (manipulação do horário do dia)</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>Os estados de humor negativos (ansiedade, raiva, confusão, depressão e fadiga) foram maiores pela manhã e o vigor foi maior à noite. Tempos de reação simples e de escolha e atenção seletiva foram melhores à noite; velocidade de arremesso e desempenho no RSA também foram melhores à noite; temperatura oral maior à noite que pela manhã e à tarde. O resumo não traz médias, DP, estatísticas de teste nem valores de p.</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="n">
+      <c r="AA25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
+      <c r="AB25" s="3" t="inlineStr">
         <is>
           <t>resumo</t>
         </is>
       </c>
-      <c r="AC26" s="2" t="inlineStr">
+      <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>• Apenas o resumo está acessível em fonte aberta: médias, testes estatísticos, correção para comparações múltiplas e versão do POMS não verificáveis.
 • O resumo não esclarece a posição do horário das 14h nas diferenças de humor.
@@ -4630,156 +4475,156 @@
 • Limitações declaradas pelos autores não constam do resumo.</t>
         </is>
       </c>
-      <c r="AD26" s="2" t="inlineStr">
+      <c r="AD25" s="3" t="inlineStr">
         <is>
           <t>O estudo indica variação diurna do humor em jovens handebolistas de elite, com humor negativo mais alto pela manhã e vigor mais alto à noite, em paralelo à melhora do desempenho cognitivo e físico e da temperatura oral ao longo do dia. A robustez não pode ser avaliada, pois o resumo não apresenta dados numéricos. A contribuição para o tema é apontar o horário da sessão como fator de confusão a controlar em medidas de humor no handebol.</t>
         </is>
       </c>
-      <c r="AE26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="210" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="AE25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="210" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>H27</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>(LUJIC; PRSKALO; BRATKO, 2023)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>LUJIC, M.; PRSKALO, I.; BRATKO, D. difference in well-being between handball players and ones not physically active. Scientific Journal of Sport and Performance, v. 2, n. 2, p. 144-150, 2023. DOI: https://doi.org/10.55860/fhsl7752.</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>• LUJIC, Marina
 • PRSKALO, Ivan
 • BRATKO, Denis</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>The difference in well-being between handball players and ones not physically active</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F26" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Scientific Journal of Sport and Performance</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2794-0586</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.55860/fhsl7752</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>Subjective well-being is a good indicator of the individual's psychological health. High levels of subjective well-being have been found in adolescents who are regularly physically active, less prone to negative emotions, more easily able to cope with life's problems and challenges, have a lower body mass index, and exhibit higher levels of life satisfaction. The participants in this research were adolescents from the Republic of Croatia, N = 756, of which 407 (53.8%) were handball players and 349 (46.2%) were adolescents from the control group not physically active. The research was conducted in elementary schools and handball clubs with adolescents in 2006 and 2007. Instruments used in this research are Life Satisfaction Scale and PANAS. Adolescent handball players are more satisfied with life, they express higher levels of positive affect and lower levels of negative affect compared to adolescents who are not involved in some form of kinesiology activities.</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Comparar o nível médio de bem-estar subjetivo (satisfação com a vida, afeto positivo e afeto negativo) entre adolescentes croatas que treinam handebol e adolescentes sem atividade física organizada, a partir da hipótese nula de ausência de diferença entre os grupos. O método menciona também a relação com traços de personalidade, que não foram medidos.</t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Observacional comparativo (os autores o denominam quase-experimental, mas a prática esportiva não foi manipulada).</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>Transversal, com aplicação única de questionários em papel e comparação entre dois grupos independentes (handebolistas e controles inativos), sem aleatorização e sem ajuste de variáveis de confusão.</t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Adolescentes croatas de 13 e 14 anos (coortes nascidas em 2006 e 2007) que treinam exclusivamente handebol em clubes ou escolas de handebol, ao menos quatro vezes por semana e há pelo menos um ano, comparados com adolescentes de escolas de ensino fundamental sem participação em atividade cinesiológica organizada; sexo não relatado; Croácia.</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>N = 756: 407 handebolistas (53,8%) e 349 controles (46,2%); taxa de resposta dos clubes de 91%; sexo, média e DP de idade e perdas não relatados.</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>Croácia</t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>• Afeto positivo: PANAS (subescala de 8 itens)
 • Afeto negativo: PANAS (subescala de 8 itens)
 • Satisfação com a vida: Escala de Satisfação com a Vida (Penezić, 1996)</t>
         </is>
       </c>
-      <c r="V27" s="3" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>• PANAS, adaptação croata de Križanić (2013), 16 itens (8 de afeto positivo e 8 de afeto negativo), escala Likert de 1 (nada) a 7 (extremamente), referência à última semana; alfa de 0,84 (afeto positivo) e 0,83 (afeto negativo) na amostra total
 • Escala de Satisfação com a Vida (Penezić, 1996), 20 itens; alfa de 0,93 na amostra total, sem atribuição explícita ao instrumento no texto</t>
         </is>
       </c>
-      <c r="W27" s="3" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>Medida única. Nos clubes, os questionários foram aplicados antes ou depois do treino, nos espaços de treino; os controles responderam em escolas de ensino fundamental (momento não detalhado). O PANAS refere-se à última semana. A coleta ocorreu sob restrições da pandemia de SARS-CoV-2.</t>
         </is>
       </c>
-      <c r="X27" s="3" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>Afeto positivo maior nos handebolistas (4,71 ± 1,06) que nos controles (4,24 ± 1,10; t = 6,07; p relatado como ,00; d = 0,42). Afeto negativo menor nos handebolistas (2,82 ± 1,03) que nos controles (3,37 ± 1,17; t = -6,95; p relatado como ,00; d = 0,48). Satisfação com a vida maior nos handebolistas (82,54 ± 11,79) que nos controles (75,02 ± 14,29; t = 7,93; p relatado como ,00; d = 0,55).</t>
         </is>
       </c>
-      <c r="Z27" s="3" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA27" s="3" t="n">
+      <c r="AA26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB27" s="3" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC27" s="3" t="inlineStr">
+      <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>• Direção causal indeterminada, admitida pelos próprios autores: adolescentes com maior bem-estar podem escolher mais o esporte.
 • Ausência de controle de sexo, nível socioeconômico, IMC e outras variáveis de confusão; sexo da amostra não relatado.
@@ -4787,30 +4632,30 @@
 • Condições de aplicação distintas entre grupos (clube, antes ou depois do treino, contra escola) e ausência de medidas repetidas.</t>
         </is>
       </c>
-      <c r="AD27" s="3" t="inlineStr">
+      <c r="AD26" s="2" t="inlineStr">
         <is>
           <t>O estudo mostra, em amostra grande de adolescentes croatas, mais afeto positivo, menos afeto negativo e maior satisfação com a vida em handebolistas que em pares inativos, com efeitos pequenos a moderados (d de 0,42 a 0,55). O delineamento transversal, sem ajuste de confusão e sem relato de sexo, não sustenta a conclusão causal dos autores. A contribuição para o tema reside na caracterização do componente afetivo do bem-estar (afeto habitual da última semana) em jovens praticantes, e não de estados de humor ligados ao treino ou à competição.</t>
         </is>
       </c>
-      <c r="AE27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="210" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="AE26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="210" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>H28</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>(MIRALLES-AMORÓS et al., 2023)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>MIRALLES-AMORÓS, L. et al. Study of Different Personalised Dietary Plans on Eating Behaviour, Body Image and Mood in Young Female Professional Handball Players: A Randomised Controlled Trial. Children, v. 10, n. 2, e259, 2023. DOI: https://doi.org/10.3390/children10020259.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>• MIRALLES-AMORÓS, Laura
 • VICENTE-MARTÍNEZ, Manuel
@@ -4824,92 +4669,92 @@
 • MARTÍNEZ-RODRÍGUEZ, Alejandro</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Study of Different Personalised Dietary Plans on Eating Behaviour, Body Image and Mood in Young Female Professional Handball Players: A Randomised Controlled Trial</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Children</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>2227-9067</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>não classificado na área</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/children10020259</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Low energy availability may precede or be caused by cognitive disturbances in professional athletes. Related psychological problems include disordered eating patterns, body shape preoccupation, depression or anxiety. The objective of this research was to evaluate the effects of different personalised dietary plans on psychological factors in young professional female handball players with low energy availability. This 12-week randomised clinical trial involved 21 female players aged 22 ± 4 years, 172.0 ± 5.4 cm and 68.4 ± 6.7 kg divided into three groups (FD: free diet; MD: Mediterranean diet; HAD: high antioxidant diet). Eating behaviour (Eating Attitude Test, EAT-26: diet, bulimia and oral control subscales), body image (Body Shape Questionnaire, BSQ) and mood state (Profile of Mode State, POMS: tension, vigour, anger, depression, fatigue) were assessed. All participants showed low energy availability (&lt;30 kcal/lean mass per day). The different plans showed no significant differences between them but significant differences over time within groups for the variables: body image, Tension, Vigour and Depression (p &lt; 0.05). Eating behaviour improved slightly but did not show statistically significant changes. Following an adequate nutritional planning for athletes seems to improve the mood and body perception of young female handball players. A longer intervention period is required to assess the differences between diets and improvement of other parameters.</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>Avaliar os efeitos de diferentes planos alimentares personalizados sobre fatores psicológicos (comportamento alimentar, imagem corporal e humor) de jovens jogadoras profissionais de handebol com baixa disponibilidade energética; de forma secundária, verificar se um padrão alimentar completo (dieta mediterrânea) melhora esses desfechos mais que o foco isolado em antioxidantes.</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>Experimental (ensaio clínico randomizado).</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>Ensaio clínico randomizado de 12 semanas com três braços paralelos (FD como controle, MD e HAD), randomização eletrônica em blocos com envelopes preparados por pesquisador externo, cegamento das participantes declarado de forma indireta e registro NCT05567211; três medidas: PRE (agosto de 2022, pré-temporada), PER (meio da intervenção) e POST (novembro de 2022, semana 12).</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>Jogadoras profissionais de handebol do sexo feminino de uma equipe espanhola de elite (campeãs da Supercopa e da Copa da Rainha da Espanha), adultas jovens, com baixa disponibilidade energética (&lt; 30 kcal/kg de massa magra por dia); Espanha.</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t>21 jogadoras (22 ± 4 anos; 172,0 ± 5,4 cm; 68,4 ± 6,7 kg; 12 h de treino semanal mais jogos), 7 por grupo: dieta livre (FD; 22 ± 4 anos), dieta mediterrânea (MD; 21 ± 3 anos) e dieta rica em antioxidantes (HAD; 22 ± 4 anos). Todas as elegíveis foram incluídas; perdas não relatadas (n = 7 por grupo nas tabelas).</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T27" s="3" t="inlineStr">
         <is>
           <t>Espanha</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="U27" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor (tensão, vigor, raiva, depressão e fadiga): POMS abreviado de 30 itens
 • Comportamento alimentar (subescalas de dieta, bulimia e preocupação com a comida, e controle oral): EAT-26
 • Imagem corporal (insatisfação corporal): Body Shape Questionnaire (BSQ) de 14 itens</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V27" s="3" t="inlineStr">
         <is>
           <t>• POMS em versão abreviada autoaplicada, 30 itens, escala Likert de 0 (nada) a 4 (muito), cinco fatores (raiva, fadiga, vigor, tensão e depressão), sem fator confusão; validação espanhola e confiabilidade não relatadas
 • Eating Attitudes Test, versão reduzida de 26 itens (EAT-26), validada em mulheres espanholas, ponto de corte de 20 pontos
@@ -4917,35 +4762,35 @@
 • Bioimpedância (Tanita BC545N) para composição corporal e IMC; estimativa da disponibilidade energética</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W27" s="3" t="inlineStr">
         <is>
           <t>Três medidas: PRE (agosto de 2022, pré-temporada), PER (meio da intervenção) e POST (novembro de 2022, semana 12). Horário e relação com treinos e jogos não relatados para o POMS.</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="X27" s="3" t="inlineStr">
         <is>
           <t>plano alimentar personalizado por 12 semanas: dieta livre com recomendações (controle), dieta mediterrânea ou dieta rica em antioxidantes (7 atletas por grupo)</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>Nenhum efeito de tempo no POMS (tensão F = 0,642, p = 0,637; vigor F = 0,288, p = 0,883; raiva F = 0,485, p = 0,747; depressão F = 0,404, p = 0,805; fadiga F = 0,153, p = 0,960) e nenhuma interação tempo × grupo (tensão F = 1,389, p = 0,265, ηp² = 0,085; vigor F = 0,869, p = 0,430, ηp² = 0,055; raiva F = 2,929, p = 0,069, ηp² = 0,163; depressão F = 1,244, p = 0,303, ηp² = 0,077; fadiga F = 2,070, p = 0,144, ηp² = 0,121). Vigor e fadiga sem diferenças. Após correção de Tukey restaram apenas duas diferenças na depressão: FD de PRE para PER (p = 0,041) e MD de PER para POST (p = 0,040); as demais diferenças de tensão, raiva e depressão só foram significativas sem correção. A depressão subiu de PRE para PER nos três grupos (FD 0,39 para 0,74; MD 0,34 para 0,60; HAD 0,26 para 0,61) e caiu em POST (FD 0,42; MD 0,18; HAD 0,31). EAT-26 sem diferenças; BSQ com diferença em MD de PRE para POST apenas sem correção (p = 0,049). Depressão correlacionou-se de forma positiva com raiva (p = 0,008), tensão (p &lt; 0,001), BSQ (p = 0,012) e EAT-26 (p &lt; 0,001); vigor correlacionou-se de forma negativa com BSQ (p = 0,015) e EAT-26 (p = 0,015). O resumo e as conclusões afirmam mudanças significativas no tempo para tensão, vigor e depressão, em contradição com a Tabela 3.</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="n">
+      <c r="AA27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
+      <c r="AB27" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AC27" s="3" t="inlineStr">
         <is>
           <t>• Amostra pequena (7 atletas por grupo), declarada pelos autores, com poder muito baixo para diferenças entre dietas.
 • Duração da intervenção possivelmente insuficiente para revelar diferenças entre planos alimentares, conforme os autores.
@@ -4953,114 +4798,114 @@
 • Momento de aplicação do POMS em relação a treinos e jogos não relatado; versão de 30 itens sem confusão e sem validação espanhola citada.</t>
         </is>
       </c>
-      <c r="AD28" s="2" t="inlineStr">
+      <c r="AD27" s="3" t="inlineStr">
         <is>
           <t>Ensaio randomizado com atletas de elite que não encontrou diferença entre dietas nem efeito de tempo significativo nas dimensões do POMS, embora o resumo e as conclusões relatem melhora do humor. A suposta melhora da depressão corresponde a aumento no meio da intervenção seguido de queda, apoiada em comparações post hoc sem correção. A robustez é baixa (n = 7 por grupo, POMS incompleto), e a contribuição para o tema consiste em indicar associações entre humor depressivo, imagem corporal e comportamento alimentar em jogadoras com baixa disponibilidade energética.</t>
         </is>
       </c>
-      <c r="AE28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="210" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="AE27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="210" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>(IVANOVIĆ; IVANOVIĆ, 2023)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>IVANOVIĆ, M.; IVANOVIĆ, U. Influence of health status and loneliness on satisfaction with life, emotional dimensions, and distress in junior handball players. Exercise and Quality of Life, v. 15, n. 1, p. 27-35, 2023. DOI: https://doi.org/10.31382/eqol.230604.</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>• IVANOVIĆ, Miroljub
 • IVANOVIĆ, Uglješa</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Influence of health status and loneliness on satisfaction with life, emotional dimensions, and distress in junior handball players</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Exercise and Quality of Life</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2406-1379, 1821-3480</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.31382/eqol.230604</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>This transversal study aimed to examine the contribution of predictor variables of the construct of health status (objective and subjective assessment of health) to the variability of the criteria satisfaction with life, emotional dimensions (positive affect, negative affect), and emotional factor of distress (depression, anxiety, and stress) in junior handball players. The pertinent sample consisted of 132 junior handball players in – Serbian First League. The average age of participants was 18.25 ± 0.90 years of age. The following measuring instruments were used: 1) the Depression, Anxiety, and Stress Scale – DASS-21, 2) De Jong Gierveld Loneliness Scale – DJGLS, 3) the Satisfaction with Life Scale‒ SWLS, and 4) The Positive and Negative Affect Schedule – PANAS showed satisfactory internal consistency. The conducted multiple regression analysis explained 51% of the proportion variance of the dependent variable satisfaction with life, positive and/or negative affectivity, and cognitive aspect of distress, where the only statistically significant negative predictors were loneliness and subjective assessment of health status. At the same time, when it comes to the assessment of loneliness in adolescents, these independent variables achieved significant interaction with the subjective assessment of health. This would mean that handball players, who subjectively assess their health as bad, and feel lonelier. On the other hand, the regression model did not confirm the role of the predictor variable objective assessment of health status and loneliness. This regression study has contributed to the existing literature and empirical data on the significance of the rarely explored relations between the constructs of health and well-being in the adolescent sports population. Theoretical contributions and practical implications for future research were also discussed.</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Examinar a contribuição da avaliação objetiva e subjetiva da saúde e da solidão para a variância da satisfação com a vida, do afeto positivo, do afeto negativo e do distresse (depressão, ansiedade e estresse) em handebolistas juniores.</t>
         </is>
       </c>
-      <c r="P29" s="3" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>Observacional.</t>
         </is>
       </c>
-      <c r="Q29" s="3" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Transversal, com aplicação única de questionários durante treino regular (fevereiro de 2023), correlação de Pearson e regressão múltipla hierárquica.</t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Handebolistas juniores de quatro clubes da Primeira Liga Oeste da Sérvia, de 17 a 21 anos, com 1,5 a 5 anos de prática; sexo não declarado; Sérvia.</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>132 jogadores; 18,25 ± 2,20 anos no método e 18,25 ± 0,90 anos no resumo (amplitude de 17 a 21); início do treino aos 14,08 ± 2,16 anos; sexo e perdas não relatados.</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>Sérvia</t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>• Afeto positivo e afeto negativo: PANAS, versão sérvia
 • Distresse (depressão, ansiedade e estresse): DASS-21
@@ -5069,7 +4914,7 @@
 • Avaliação subjetiva da saúde: item único</t>
         </is>
       </c>
-      <c r="V29" s="3" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>• PANAS, versão sérvia (Mihić et al., 2014), duas escalas de 10 itens, Likert de 5 pontos, referência aos últimos dias; alfa de 0,85 (afeto positivo) e 0,88 (afeto negativo)
 • DASS-21 (21 itens; alfa de 0,88 a 0,90 nas subescalas e 0,90 no total)
@@ -5078,35 +4923,35 @@
 • Avaliação objetiva da saúde (lista de 11 doenças crônicas) e item único de saúde subjetiva (escala de 4 pontos)</t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>Aplicação única durante treino regular de handebol, em fevereiro de 2023. O PANAS refere o humor dos últimos dias ("last couple of days"); o DASS-21 refere a última semana.</t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>Descritivos: afeto positivo 15,08 ± 3,25; afeto negativo 7,05 ± 3,01; distresse 14,98 ± 10,03; solidão 16,67 ± 5,01. Correlações: afeto positivo com afeto negativo r = 0,50; saúde objetiva com afeto negativo r = 0,32; satisfação com a vida com afeto negativo r = 0,27. Modelo com saúde objetiva: solidão predisse afeto positivo (β = 0,29) e afeto negativo (β = 0,27); saúde objetiva não predisse os afetos (β = -0,09 e -0,10); R = 0,40 (R² corrigido = 0,13) e R = 0,38 (R² corrigido = 0,17). Modelo com saúde subjetiva: solidão predisse afeto positivo (β = -0,32) e afeto negativo (β = -0,28); saúde subjetiva predisse afeto positivo (β = -0,13), com interação saúde subjetiva × solidão (β = 0,19). Solidão predisse satisfação com a vida (β = -0,44 e -0,29) e distresse (β = 0,37 e 0,40). As notas das tabelas trazem *p ≤ 0,01 e p ≤ 0,05 (ordem invertida), e o sinal dos β da solidão muda entre as tabelas. O resumo informa 51% de variância explicada, valor que corresponde ao R múltiplo.</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA29" s="3" t="n">
+      <c r="AA28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB29" s="3" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC29" s="3" t="inlineStr">
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>• Os autores reconhecem que as conclusões sobre juniores sérvios seriam mais realistas com amostra maior.
 • Delineamento transversal e autorrelato, sem inferência causal.
@@ -5114,30 +4959,30 @@
 • Inconsistências internas (sinais dos coeficientes, notas de significância e matriz de correlação incompleta) que exigem replicação.</t>
         </is>
       </c>
-      <c r="AD29" s="3" t="inlineStr">
+      <c r="AD28" s="2" t="inlineStr">
         <is>
           <t>O estudo associa a solidão e a saúde subjetiva aos afetos positivo e negativo, à satisfação com a vida e ao distresse em handebolistas juniores sérvios. As múltiplas inconsistências entre texto e tabelas, a inversão de sinais dos coeficientes e a interpretação de R como variância explicada comprometem fortemente a confiabilidade dos achados. A contribuição para o tema é apenas exploratória, ao sugerir fatores sociais e de saúde percebida como correlatos do afeto habitual em jovens jogadores.</t>
         </is>
       </c>
-      <c r="AE29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30" ht="210" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="AE28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="210" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>N4</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>(MORENAS-AGUILAR et al., 2023)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>MORENAS-AGUILAR, M. et al. The menstrual cycle does not influence vertical jump performance or throwing velocity in amateur team handball players. Science &amp;amp; Sports, v. 38, n. 2, p. 211-215, 2023. DOI: https://doi.org/10.1016/j.scispo.2022.02.008.</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>• MORENAS-AGUILAR, M. D.
 • CUPEIRO, R.
@@ -5146,91 +4991,91 @@
 • GARCIA-RAMOS, A.</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>The menstrual cycle does not influence vertical jump performance or throwing velocity in amateur team handball players</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Science &amp; Sports</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>0765-1597</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.scispo.2022.02.008</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>(1) Objectives: This study aimed to compare physical performance (countermovement jump height and throwing velocity) and psychological traits (mood state and perceived pain) across the menstrual cycle. (2) Equipment and methods: Eight women from an amateur handball team (age = 19.8 ± 1.9 years) were tested during two months at three time points of the menstrual cycle (early follicular phase, late follicular phase, and mid-luteal phase) (i.e., six testing sessions). The calendar-based and the urinary luteinizing hormone methods were used in combination to detect the phase of the menstrual cycle. Two questionnaires were administered at the beginning of each testing session to assess the mood state (Self-Assessment Manikin scale for Valence) and perceived pain (Visual Analogic Scale Pain scale) and, afterwards, the countermovement jump height and throwing velocity were evaluated. (3) Results: The main results showed no significant differences between the phases of the menstrual cycle for countermovement jump height (p = 0.708), throwing velocity (p = 0.305), Self-Assessment Manikin scale for Valence (p = 0.639) or Visual Analogic Scale Pain scale (p = 0.565). These results suggest that the performance of explosive lower-body and upper-body tasks is not affected across the menstrual cycle in young athletes whose mood and perceived pain are also unaffected by these hormonal fluctuations.</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>Comparar o desempenho físico (altura do salto com contramovimento e velocidade de arremesso) e traços psicológicos (estado de humor e dor percebida) entre fases do ciclo menstrual em jogadoras amadoras de handebol.</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>Observacional.</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>Longitudinal intrassujeito com medidas repetidas em três fases do ciclo menstrual (folicular inicial, folicular tardia e lútea média) em dois ciclos (seis sessões por jogadora), de novembro de 2019 a fevereiro de 2020; questionários no início de cada sessão, antes do aquecimento e dos testes.</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>Jogadoras de uma equipe sênior amadora de handebol, adultas jovens, com ciclo menstrual regular e sem contraceptivo oral nos 6 meses anteriores; país não declarado.</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t>12 jogadoras recrutadas; 4 excluídas por distúrbios menstruais (3 ciclos irregulares e 1 anovulatório); 8 analisadas: 19,8 ± 1,9 anos; 67,6 ± 15,1 kg; 167 ± 5,6 cm.</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T29" s="3" t="inlineStr">
         <is>
           <t>Não relatado</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="U29" s="3" t="inlineStr">
         <is>
           <t>• Estado de humor (valência): Self-Assessment Manikin (SAM), escala de valência
 • Dor percebida: escala visual analógica (EVA)</t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V29" s="3" t="inlineStr">
         <is>
           <t>• Self-Assessment Manikin (SAM), escala de valência, item pictórico único; escala de resposta e confiabilidade não relatadas
 • Escala visual analógica de dor (EVA)
@@ -5238,35 +5083,35 @@
 • Método de calendário combinado com teste urinário de hormônio luteinizante para identificar as fases do ciclo</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="W29" s="3" t="inlineStr">
         <is>
           <t>Questionários aplicados no início de cada sessão de teste, antes do aquecimento padronizado e dos testes de salto e arremesso; seis sessões por jogadora (três fases em dois ciclos).</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="X29" s="3" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>O teste de Friedman não mostrou diferença na valência do SAM entre as fases do ciclo menstrual (p = 0,639). Dor percebida sem diferença (p = 0,565). Altura do salto (p = 0,708) e velocidade de arremesso (p = 0,305) sem efeito da fase. Médias, DP e tamanhos de efeito do SAM constam da Tabela 1 e da Figura 1, ausentes da versão aberta.</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z29" s="3" t="inlineStr">
         <is>
           <t>Sem efeito</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="n">
+      <c r="AA29" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
+      <c r="AB29" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC30" s="2" t="inlineStr">
+      <c r="AC29" s="3" t="inlineStr">
         <is>
           <t>• Amostra pequena (8 mulheres), principal limitação declarada pelos autores.
 • Exclusão de 33,3% das recrutadas por distúrbios menstruais, também apontada pelos autores.
@@ -5274,30 +5119,30 @@
 • Fases do ciclo não confirmadas por dosagem sérica de estrogênio e progesterona.</t>
         </is>
       </c>
-      <c r="AD30" s="2" t="inlineStr">
+      <c r="AD29" s="3" t="inlineStr">
         <is>
           <t>O estudo não encontrou variação da valência afetiva, da dor percebida nem do desempenho explosivo entre fases do ciclo menstrual em jogadoras amadoras de handebol. Com 8 participantes, item único de valência e ausência dos descritivos na versão aberta, o resultado nulo tem baixa robustez. A contribuição para o tema é inicial, ao sugerir que o ciclo menstrual não altera de forma marcante o tom afetivo pré-sessão nessa população.</t>
         </is>
       </c>
-      <c r="AE30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31" ht="210" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="AE29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="210" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>H29</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>(SAHLI et al., 2024)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>SAHLI, F. et al. Enhancing Skills, Mood, and Performance in Overweight Handball Players: Exploring Individual vs. Collective Verbal Encouragement Strategies. Children, v. 11, n. 4, e432, 2024. DOI: https://doi.org/10.3390/children11040432.</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>• SAHLI, Faten
 • BOUZOURAA, Mohamed Mansour
@@ -5310,125 +5155,125 @@
 • ZGHIBI, Makram</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Enhancing Skills, Mood, and Performance in Overweight Handball Players: Exploring Individual vs. Collective Verbal Encouragement Strategies</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Children</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2227-9067</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>não classificado na área</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/children11040432</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>This comparative study investigates the effectiveness of two teaching methods, individual verbal encouragement and collective verbal encouragement, in enhancing the technical–tactical skills and mood state of obese students during handball matches. This study employs a randomized controlled design and involves 28 overweight students (50% females), age: 17.4 ± 2.08 years and BMI: 26.8 ± 1.5 for females and 27.3 ± 2.1 for males. Technical–tactical skills are assessed through performance metrics (individual evaluation proposal by Gréhaigne) such as Ball Played (BP), Conquered Ball (CB), Lost Ball (LB), Shoots/Goals, Conservation index, and defensive index, while mood states are evaluated using pre- and post-tests (BRUMS Scale). Results reveal that individual verbal encouragement significantly enhances technical–tactical skills and positively influences the mood state of overweight students compared to collective verbal encouragement. Boys in Session 1 with VEI displayed a significantly higher number of ball plays (mean difference = 0.94 standard deviations, p = 0.004) and conquered balls (mean difference = 0.78 standard deviations, p = 0.006) compared to VEC. They also had a lower number of Lost Balls (mean difference = −0.62 standard deviations, p = 0.018) and a higher shooting efficiency (Shoots/Goals ratio, mean difference = 0.67 standard deviations; p = 0.013). Similar trends were observed in Session 2, with VEI, again, demonstrating advantages. Girls exhibited analogous improvements with VEI in both sessions. Notably, these performance enhancements coincided with positive emotional changes, with VEI leading to a greater decrease in depression and fatigue scores for both boys and girls. The study highlights the importance of tailoring teaching methods to the specific needs of overweight students in the context of handball, emphasizing the effectiveness of individualized verbal encouragement for skill development and emotional well-being. These findings offer practical implications for educators and coaches involved in physical education, advocating for personalized approaches to optimize learning experiences for overweight students in sports settings.</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Investigar a eficácia de duas estratégias de ensino, o encorajamento verbal individual (VEI) e o encorajamento verbal coletivo (VEC), sobre as habilidades técnico-táticas e os estados de humor de estudantes com sobrepeso durante jogos de handebol.</t>
         </is>
       </c>
-      <c r="P31" s="3" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>Experimental (declarado randomizado e controlado; procedimento de aleatorização não descrito).</t>
         </is>
       </c>
-      <c r="Q31" s="3" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>Dois grupos paralelos (VEI e VEC), duas sessões com dois tempos de 12 min de jogo 7 contra 7; BRUMS antes e depois (descrição divergente quanto ao momento exato); análise de variância de medidas repetidas 2 (grupo) × 2 (momento), separada por sexo.</t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Estudantes do ensino secundário com sobrepeso, de ambos os sexos, em jogos de handebol no contexto escolar (escola Ahmed Amara, região de Kef); não são atletas federados; Tunísia.</t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>28 estudantes (14 meninos e 14 meninas; 17,4 ± 2,08 anos). Meninos: 17,5 ± 2,4 anos; 89,7 ± 1,6 kg; 173,2 ± 1,5 cm; IMC 27,3 ± 2,1. Meninas: 17,3 ± 1,7 anos; 88,2 ± 2,6 kg; 164,3 ± 2,7 cm; IMC 26,8 ± 1,5. Análise de poder a priori: N = 22. Tamanho de cada grupo (VEI e VEC) e perdas não relatados.</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>Tunísia</t>
         </is>
       </c>
-      <c r="U31" s="3" t="inlineStr">
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>• Estados de humor (tensão, depressão, raiva, vigor, fadiga e confusão): BRUMS, versão árabe de 24 itens</t>
         </is>
       </c>
-      <c r="V31" s="3" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>• Brunel Mood Scale (BRUMS), versão árabe, 24 itens, seis subescalas, escala de 0 (nada) a 4 (extremamente), escore de 0 a 16 por subescala; alfa nesta amostra de 0,839 (fadiga) a 0,912 (vigor)
 • Proposta de avaliação individual de Gréhaigne (bolas jogadas, bolas conquistadas, bolas perdidas, arremessos/gols, índice de conservação e índice defensivo), por análise de vídeo
 • Medidas antropométricas (massa, estatura, IMC)</t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>Descrições divergentes: na seção do instrumento, o BRUMS foi aplicado "immediately after each session"; no procedimento, "both before and after each session, including pre- and post-tests for each bout". A Tabela 2 apresenta apenas pré e pós por grupo e sexo, sem indicar a sessão.</t>
         </is>
       </c>
-      <c r="X31" s="3" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>encorajamento verbal individual do professor (VEI) contra encorajamento verbal coletivo durante o jogo (VEC), em duas sessões de jogos 7x7 de handebol</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>Interação grupo × tempo favorável ao VEI em todas as dimensões. Meninos: depressão de 6,35 ± 1,00 para 3,28 ± 1,54 no VEI e de 6,22 ± 1,42 para 5,42 ± 1,50 no VEC (F = 11,99; η² = 0,31; p = 0,002); fadiga de 7,29 ± 0,89 para 3,71 ± 1,58 no VEI e de 7,14 ± 1,09 para 5,92 ± 1,49 no VEC (F = 10,69; η² = 0,29; p = 0,003); confusão F = 9,31, η² = 0,26, p = 0,005; tensão F = 5,82, η² = 0,18, p = 0,023; raiva F = 8,86, η² = 0,25, p = 0,006; vigor de 8,35 ± 1,15 para 10,64 ± 1,33 no VEI e de 6,85 ± 1,40 para 7,64 ± 1,44 no VEC (F = 7,69; η² = 0,22; p = 0,010). Meninas: depressão de 7,85 ± 1,02 para 4,28 ± 2,05 no VEI e de 7,38 ± 6,33 para 6,33 ± 1,90 no VEC (F = 30,20; η² = 0,53); fadiga F = 24,81, η² = 0,48; confusão F = 32,09, η² = 0,55; raiva F = 13,54, η² = 0,34 (todos p = 0,001); tensão F = 6,48, η² = 0,20, p = 0,017; vigor de 8,92 ± 1,73 para 11,42 ± 1,28 no VEI e de 7,57 ± 1,78 para 8,07 ± 1,67 no VEC (F = 6,80; η² = 0,20; p = 0,015). Habilidades técnico-táticas superiores no VEI (meninos, sessão 1: bolas jogadas d = 0,94, p = 0,004; bolas conquistadas d = 0,78, p = 0,006; bolas perdidas d = -0,62, p = 0,018; arremessos/gols d = 0,67, p = 0,013; meninas: d de 0,48 a 0,93).</t>
         </is>
       </c>
-      <c r="Z31" s="3" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA31" s="3" t="n">
+      <c r="AA30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC31" s="3" t="inlineStr">
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>• Generalização restrita a estudantes com sobrepeso e amostra pequena, conforme os autores.
 • Dependência de autorrelato e de dados observacionais sujeitos a viés, declarada pelos autores.
@@ -5436,30 +5281,30 @@
 • Tipo de encorajamento confundido com o momento de sua aplicação (antes e nos intervalos no VEI; durante o jogo no VEC) e aleatorização não descrita.</t>
         </is>
       </c>
-      <c r="AD31" s="3" t="inlineStr">
+      <c r="AD30" s="2" t="inlineStr">
         <is>
           <t>O estudo relata efeitos grandes do encorajamento verbal individual sobre a redução de humor negativo e o aumento do vigor em escolares com sobrepeso, com η² de 0,18 a 0,55. A robustez é limitada por aleatorização não descrita, confusão entre tipo e momento do encorajamento, graus de liberdade incompatíveis com a análise por sexo, aprovação ética posterior à coleta e possíveis erros de digitação. A contribuição para o tema é indicar o clima motivacional verbal do professor como modulador agudo do humor em handebol escolar, não em atletas.</t>
         </is>
       </c>
-      <c r="AE31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32" ht="210" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="AE30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="210" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>H30</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>(AKROUSH et al., 2025)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>AKROUSH, S. et al. Psychological mood patterns among Jordanian handball players. Retos, n. 62, p. 285-294, 2025. DOI: https://doi.org/10.47197/retos.v62.109407.</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>• AKROUSH, Sofia Hwaishel
 • ALKASASBEH, Walaa
@@ -5468,123 +5313,123 @@
 • KHATATBEH, Mu’tasem</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Psychological mood patterns among Jordanian handball players</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Retos</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>1988-2041, 1579-1726</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.47197/retos.v62.109407</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>The purpose of this study was to identify the prevailing mood patterns amongst handball players in Jordan. Therefore, this descriptive study was conducted on a sample consisting of (76) male handball players participating in the 2022/2023 Jordanian Handball League championship. The list of mood patterns for athletes was used as a data collection tool along with the following three statistical methods: Arithmetic mean, Standard deviations, and Two-Way ANOVA. The study results showed that the personal flexibility pattern emerged in first place with a high level and an arithmetic average of (2.3728). The cease operations pattern emerged second with a high level and an arithmetic average of (2.2556). The excitement operations pattern emerged third with a high level and an arithmetic average of (2.2257). Results relatively exhibited that there were no statistically significant differences in the level of mood patterns according to the variable of experience and player position amongst handball players. The researchers suggested a number of recommendations including, raising the awareness of handball players on psychological importance; in addition to mood preparation prior to the competitions. It is advised that players take courses and educational workshops that can be offered to athletes to enhance their psychological and physical performance Especially courses in regard to the excitement operations pattern, which obtained the lowest order among the three mood patterns.</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>Identificar os padrões de humor predominantes entre jogadores de handebol da Jordânia e verificar diferenças desses padrões conforme o tempo de experiência e a posição de jogo.</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>Observacional descritivo.</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>Transversal, com medida única durante o campeonato da liga 2022/2023, em quatro ginásios, e comparação entre subgrupos de posição e de experiência (análise de variância de dois fatores sem termo de interação, apenas para o escore total).</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>Jogadores de handebol do sexo masculino participantes da liga jordaniana de handebol 2022/2023 (nível nacional); Jordânia.</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t>76 jogadores selecionados de forma aleatória de uma população de 112. Posição: armadores 40 (52,6%), pontas e pivôs 27 (35,5%), goleiros 9 (11,8%). Experiência: menos de 10 anos 45 (59,2%); 10 anos ou mais 31 (40,8%). Idade e perdas não relatadas.</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T31" s="3" t="inlineStr">
         <is>
           <t>Jordânia</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U31" s="3" t="inlineStr">
         <is>
           <t>• Padrões de humor (força dos processos de excitação, força dos processos de cessação e flexibilidade pessoal): Lista de padrões de humor para atletas (Allawi, 1998)</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V31" s="3" t="inlineStr">
         <is>
           <t>• Lista de padrões de humor para atletas (Allawi, 1998), de origem árabe, 30 itens na forma original em três dimensões de 10 itens, escala de 3 pontos (3 = concordo fortemente; 2 = moderadamente; 1 = pouco); forma final de 20 itens, sem indicação dos itens retirados; correlação dimensão-total de 0,650, 0,893 e 0,771; alfa de Cronbach de 0,750</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W31" s="3" t="inlineStr">
         <is>
           <t>n.r. Coleta durante a liga 2022/2023, sem indicação do momento em relação a treinos ou jogos e sem período de referência das respostas.</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="X31" s="3" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>Flexibilidade pessoal M = 2,3728 ± 0,45450 (1º lugar, nível alto); cessação M = 2,2556 ± 0,37349 (2º lugar, alto); excitação M = 2,0695 ± 0,34086 (3º lugar, alto); escore total M = 2,2257 ± 0,29365 (o resumo atribui 2,2257 à excitação). Armadores 2,2200 ± 0,26646; pontas e pivôs 2,2463 ± 0,32223; goleiros 2,1889 ± 0,34891; experiência inferior a 10 anos 2,2044 ± 0,28620; 10 anos ou mais 2,2565 ± 0,30625. Sem diferença por posição (F = 0,077; p = 0,926) nem por experiência (F = 0,432; p = 0,513); modelo corrigido F = 0,238, p = 0,870, R² = 0,010.</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z31" s="3" t="inlineStr">
         <is>
           <t>Sem efeito</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="n">
+      <c r="AA31" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
+      <c r="AB31" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AC31" s="3" t="inlineStr">
         <is>
           <t>• Uso exclusivo de questionário de autorrelato, sujeito a imprecisão e viés de memória, conforme os autores.
 • Instrumento centrado em propriedades do sistema nervoso (excitação, inibição e mobilidade), próximo do temperamento, sem medida de estados de humor transitórios.
@@ -5592,30 +5437,30 @@
 • Ausência de análise por dimensão, de tamanho de efeito e de comparação com outras populações.</t>
         </is>
       </c>
-      <c r="AD32" s="2" t="inlineStr">
+      <c r="AD31" s="3" t="inlineStr">
         <is>
           <t>O estudo descreve escores elevados nas três dimensões de padrões de humor em jogadores da liga jordaniana, sem diferenças por posição ou experiência. A validação mínima do instrumento reduzido, a ausência de idade e de momento da coleta e a incoerência entre resumo e tabela limitam a robustez. A contribuição para o tema é marginal, pois o construto medido se aproxima de características temperamentais e não de estados de humor como os avaliados por POMS ou BRUMS.</t>
         </is>
       </c>
-      <c r="AE32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33" ht="210" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="AE31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="210" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>H31</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>(BATALLA-GAVALDA et al., 2025)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BATALLA-GAVALDA, A. et al. Mayor validez ecológica del Game-Based Performance Test en comparación con el Yo-Yo IR1 en jugadoras de balonmano amateur. Journal of Sport and Health Research, v. 17, n. Supl. 2, p. 178-196, 2025. DOI: https://doi.org/10.58727/jshr.118640.</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>• BATALLA-GAVALDA, Abraham
 • BELTRÁN-GARRIDO, Jose Vicente
@@ -5625,92 +5470,92 @@
 • DAZA-SOBRINO, Gabriel</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Mayor validez ecológica del Game-Based Performance Test en comparación con el Yo-Yo IR1 en jugadoras de balonmano amateur (título em inglês: Superior Ecological Validity from the Game-Based Performance Test Compared to the Yo-Yo IR1 in Women's Amateur Handball Players)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Journal of Sport and Health Research</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>1989-6239</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.58727/jshr.118640</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>Objectives: To evaluate the ability of the Yo-Yo Intermittent Recovery Test level 1 (YYIRT-1) and the Game-Based Performance Test (GBPT) to reproduce the psychophysiological and metabolic responses observed during official matches in amateur handball players. Methods: Sixteen players (21.9 ± 3.2 years old) from the Catalan Women's Senior League (Catalonia, Spain) completed both tests during the preseason and in ten consecutive official matches. Cardiovascular, perceptual and physiological-metabolic variables were analyzed using linear mixed models. Results: Both tests achieved maximum heart rates similar to competition, but only the GBPT replicated the temporal distribution in the moderate and high zones. The RPE was higher in both tests than in the matches; the YYIRT-1 produced a more negative mood profile than the GBPT and the competition. Blood lactate was higher in the tests (GBPT: 8.8 mmol· L⁻¹; YYIRT-1: 10.2 mmol· L⁻¹) than in matches (3.9 mmol· L⁻¹). Body mass loss was greater in competition (1.18%) than in GBPT (0.15%) and YYIRT-1 (0.31%). Players spent 21.9% of live time above the maximum heart rate reached in the YYIRT-1, and 4.5% in the GBPT. Conclusions: The GBPT showed greater ecological validity, better reproducing competitive demands, while the YYIRT-1 overestimated low-intensity exposure and induced greater supramaximal and psychological stress.</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Avaliar a capacidade do Yo-Yo Intermittent Recovery Test nível 1 (YYIRT-1) e do Game-Based Performance Test (GBPT) de reproduzir as respostas psicofisiológicas e metabólicas observadas em jogos oficiais de jogadoras amadoras de handebol.</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Observacional com medidas repetidas (comparação intrassujeito entre condições).</t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Medidas repetidas em duas fases: pré-temporada, com YYIRT-1 e GBPT em sessões separadas por 48 h (ordem do primeiro teste sorteada, com descrição contraditória no texto), e período competitivo, com monitoramento de 10 jogos oficiais consecutivos; POMS e PSS aplicados antes de cada teste e de cada jogo; modelos lineares mistos com intercepto aleatório por jogadora.</t>
         </is>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Jogadoras amadoras de handebol do sexo feminino, adultas jovens, da categoria regional máxima da Catalunha (Liga Catalana Sénior Femenina); Espanha.</t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>16 jogadoras (21,93 ± 3,25 anos; 1,66 ± 0,06 m; 64,36 ± 13,86 kg; gordura de 20,19 ± 3,37%; experiência de 10,44 ± 1,86 anos; quatro treinos de 2 h por semana e um jogo no fim de semana). Perdas não relatadas; modelos mistos com todos os dados disponíveis. Mesma amostra de H32.</t>
         </is>
       </c>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>Espanha</t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>• Estados de humor (tensão-ansiedade, depressão-desânimo, raiva-hostilidade, vigor-atividade, fadiga-inércia, confusão-desorientação e PTH): POMS, versão espanhola de 58 itens
 • Estresse percebido: Perceived Stress Scale (PSS), versão espanhola de 14 itens
 • Percepção subjetiva de esforço: escala de Borg 6-20</t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>• POMS, versão espanhola (Balaguer et al., 1993), 58 itens, escala de 0 a 4, dois itens invertidos; PTH = soma das subescalas negativas menos vigor mais 100; confiabilidade na amostra não relatada
 • Perceived Stress Scale (PSS), versão espanhola (Remor, 2006), 14 itens
@@ -5719,35 +5564,35 @@
 • Testes de campo YYIRT-1 e GBPT</t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>Conforme a Tabela 1, PSS e POMS foram aplicados antes de cada teste de campo (YYIRT-1 e GBPT) e antes de cada um dos 10 jogos oficiais; a PSE (Borg 6-20) foi registrada 30 min após cada teste e jogo. Período de referência do POMS não relatado.</t>
         </is>
       </c>
-      <c r="X33" s="3" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>não se aplica (comparação entre Yo-Yo IR1, Game-Based Performance Test e jogo oficial)</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>Médias (jogo; GBPT; YYIRT-1): tensão 10,17 ± 4,87; 9,69 ± 3,50; 11,56 ± 6,89. Depressão 7,74 ± 8,47; 6,50 ± 5,96; 11,63 ± 10,90 (YYIRT-1 maior que jogo, d = 0,18, IC 95% 0,02 a 0,35). Raiva 8,03 ± 6,10; 8,44 ± 5,35; 10,13 ± 6,32. Vigor 10,78 ± 4,52; 12,56 ± 3,67 (GBPT maior que jogo, d = 0,17, IC 95% 0,01 a 0,33); 10,50 ± 2,85. Fadiga 6,02 ± 4,28; 6,00 ± 3,06; 9,31 ± 6,23 (YYIRT-1 maior, d = 0,30, IC 95% 0,14 a 0,47). Confusão 5,93 ± 3,61; 5,88 ± 2,85; 7,00 ± 3,76. PTH 127,12 ± 23,01; 123,94 ± 14,78; 139,13 ± 29,94 (YYIRT-1 maior, d = 0,22, IC 95% 0,06 a 0,38). Estresse percebido 29,07 ± 8,28; 26,63 ± 5,14; 30,31 ± 10,67, sem diferença. PSE maior nos testes que no jogo (jogo 14,29 ± 3,23; GBPT 16,94 ± 1,73, d = 0,30; YYIRT-1 16,69 ± 1,40, d = 0,28). Lactato pós maior nos testes (GBPT 8,75 ± 2,31; YYIRT-1 10,21 ± 2,73) que no jogo (3,85 ± 1,49).</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
-      <c r="AA33" s="3" t="n">
+      <c r="AA32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC33" s="3" t="inlineStr">
+      <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>• Ausência de seção de limitações; os autores indicam como necessária a validação em amostras maiores e mais heterogêneas.
 • Nutrição, sono e monitoramento avançado não controlados, apontados pelos autores como objeto de pesquisa futura.
@@ -5755,34 +5600,34 @@
 • Cada teste medido uma única vez contra 10 jogos e padronização dos tamanhos de efeito não explicitada.</t>
         </is>
       </c>
-      <c r="AD33" s="3" t="inlineStr">
+      <c r="AD32" s="2" t="inlineStr">
         <is>
           <t>O estudo compara o humor prévio a dois testes de campo e a jogos oficiais em jogadoras amadoras e encontra perfil mais negativo antes do YYIRT-1 (mais depressão, fadiga e PTH) e vigor levemente maior antes do GBPT, com efeitos triviais a pequenos. Como o POMS antecede os testes, a interpretação de que o YYIRT-1 induziu humor negativo não decorre do desenho, e a amostra pequena coincide com a de H32. A contribuição é mostrar que o contexto avaliativo (teste contra jogo) se associa a diferenças modestas no estado de humor pré-esforço.</t>
         </is>
       </c>
-      <c r="AE33" s="3" t="inlineStr">
+      <c r="AE32" s="2" t="inlineStr">
         <is>
           <t>amostra também descrita em H32</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="210" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33" ht="210" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>(AYDI et al., 2025)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>AYDI, B. et al. Empowering Obese Children in Physical Education: Exploring the Influence of Verbal Encouragement on Games Intensity, Mood States, and Physical Enjoyment during Passing Games. PLOS ONE, v. 20, n. 4, e0319414, 2025. DOI: https://doi.org/10.1371/journal.pone.0319414.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>• AYDI, Bilel
 • SELMI, Okba
@@ -5796,92 +5641,92 @@
 • SOUISSI, Nizar</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Empowering Obese Children in Physical Education: Exploring the Influence of Verbal Encouragement on Games Intensity, Mood States, and Physical Enjoyment during Passing Games</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>PLOS ONE</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>1932-6203</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1371/journal.pone.0319414</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>This study aimed to assess the impact of physical education teachers’ verbal encouragements on the psychophysiological aspects, physical enjoyment, and mood states of obese children (OC) in a physical education context. Sixteen OC students (mean age = 13.81 ± 0.73 years) from a preparatory school participated in two test sessions, conducted in a randomized order. Each session involved a series of passing games (games of 10 successive passes) with and without verbal encouragement, with a one-week interval between sessions. The games, formatted as 3 vs. 3 with two additional obese joker’ players, lasted 18 minutes. Each game comprised four 3-minute active periods interspersed with 2-minute passive recovery bouts, played on a 10 × 20-m pitch. Heart rate was continuously measured throughout each session. Additionally, the Brunel Mood Scale (BMS) was assessed before and after the PG. Furthermore, rating of perceived exertion (OMNI-RPE) and physical activity enjoyment (PACES) were assessed after the testing sessions. Video analysis was used to quantify technical actions during PG. PGs with VE induced higher HR (% maximum HR and mean HR), OMNI-RPE, and PACES scores than PGs without VE (ES=−1.51, ES=−0.78, ES=−0.73, ES=2.07, respectively). Compared with PGs without VE, SSGs with VE resulted in an increased percentage of successful passes, number of Goal (10 passes) and fewer lost balls (ES=O.70, ES=−0.54, ES=−0.86, respectively). The PGVE trial also showed higher vigor and lower total mood disturbance (TMD) compared to the PGNVE trial (ES = −1.11, d = 0.78, respectively). Physical education teachers are encouraged to incorporate joker exercises with verbal encouragement to enhance game intensity, mood state, physical enjoyment and technical performance during games among OCs.</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>Avaliar o efeito do encorajamento verbal do professor de educação física sobre a intensidade do jogo, os aspectos psicofisiológicos, o prazer na atividade física e os estados de humor de crianças obesas em jogos de passes.</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>Experimental.</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>Cruzado com duas condições (jogo de passes com e sem encorajamento verbal) em ordem aleatória e contrabalançada, com uma semana de intervalo; jogo 3 contra 3 com dois coringas, quatro blocos de 3 min com 2 min de recuperação passiva; BRUMS antes e depois de cada jogo.</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>Meninos obesos (IMC &gt; 30 kg/m²) do 7º e 8º anos de escola preparatória, em aulas regulares de educação física, em jogo de passes baseado nas regras do handebol; não são atletas de handebol; Tunísia.</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>16 meninos obesos: 13,81 ± 0,73 anos; 162 ± 4,18 cm; 79,75 ± 3,75 kg; gordura corporal de 30,56 ± 0,53%. Tamanho amostral calculado: 11. Perdas não relatadas.</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>Tunísia</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor (vigor, fadiga, depressão, confusão, tensão, raiva e PTH): Brunel Mood Scale (BRUMS) de 24 itens
 • Prazer na atividade física: Physical Activity Enjoyment Scale (PACES) de 8 itens
 • Percepção subjetiva de esforço: escala OMNI-RPE (0 a 10)</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t>• Brunel Mood Scale (BRUMS), 24 itens, escala de 0 (nada) a 4 (extremamente), seis dimensões; PTH = (fadiga + raiva + confusão + tensão + depressão) menos vigor, mais 100; alfa de 0,87 a 0,93; o texto também denomina o instrumento POMS
 • Physical Activity Enjoyment Scale (PACES), 8 itens, escala de 7 pontos, escore de 8 a 56
@@ -5889,35 +5734,35 @@
 • Frequência cardíaca (Polar Team Sport System), teste VAMEVAL para FC máxima e análise de vídeo das ações técnicas</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t>BRUMS aplicado antes e depois de cada jogo de passes nas duas condições; PSE (OMNI-RPE) logo após e PACES 5 min após cada sessão; FC monitorada durante o jogo.</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t>Jogo de passes 3 x 3 com dois coringas obesos (10 passes seguidos, regras do handebol, 4 x 3 min, campo de 20 x 10 m), com ou sem encorajamento verbal do professor, em ordem aleatória e contrabalançada, com uma semana de intervalo.</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>A variação do vigor foi maior no jogo com encorajamento verbal (p = 0,01; ES = -1,51 nos resultados e -1,11 no resumo) e a variação da PTH foi menor com encorajamento (p = 0,02; ES = 0,78). Tensão, raiva, confusão, depressão e fadiga não diferiram entre condições (p &gt; 0,05). Com encorajamento, %FCmáx (ES = -1,51), FC média (ES = -0,78), PSE (ES = -0,73) e PACES (ES = 2,07) foram maiores, com mais passes certos (ES = 0,70), menos bolas perdidas (ES = -0,54) e mais gols de 10 passes. As médias e os DP do humor aparecem apenas em figura.</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="n">
+      <c r="AA33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AB33" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AC33" s="3" t="inlineStr">
         <is>
           <t>• Amostra pequena, pela dificuldade de recrutar crianças obesas com o mesmo professor, conforme os autores.
 • Participação exclusiva de meninos com menos de 14 anos, sem diversidade de sexo e idade, declarada pelos autores.
@@ -5925,155 +5770,155 @@
 • Ausência de cegamento do professor, que também coletou os dados, e possíveis erros de transcrição dos tamanhos de efeito do humor.</t>
         </is>
       </c>
-      <c r="AD34" s="2" t="inlineStr">
+      <c r="AD33" s="3" t="inlineStr">
         <is>
           <t>O estudo mostra que o encorajamento verbal do professor durante jogos de passes com regras do handebol eleva o vigor e reduz a PTH de meninos obesos, junto com maior intensidade, prazer e desempenho técnico. A robustez é limitada pela amostra pequena, pela ausência de cegamento e pela coincidência numérica dos tamanhos de efeito do humor com os da frequência cardíaca. A contribuição para o tema é transferir para o contexto escolar a evidência de que o encorajamento verbal modula o humor agudo em tarefas derivadas do handebol.</t>
         </is>
       </c>
-      <c r="AE34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35" ht="210" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="AE33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="210" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>N8</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>(DIACHENKO; TYSHCHENKO, 2025)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>DIACHENKO, M.; TYSHCHENKO, V. Psycho-emotional regulation of female handball players during training. Scientific Journal of National Pedagogical Dragomanov University. Series 15: Scientific and Pedagogical Problems of Physical Culture (Physical Culture and Sports), n. 5K(191), p. 66-70, 2025. DOI: https://doi.org/10.31392/udu-nc.series15.2025.05k(191).13.</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>• DIACHENKO, Mykhailo
 • TYSHCHENKO, Valeria</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Psycho-emotional Regulation of Female Handball Players During Training</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Scientific Journal of National Pedagogical Dragomanov University. Series 15. Scientific and pedagogical problems of physical culture (physical culture and sports)</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>2311-2220</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.31392/udu-nc.series15.2025.05k(191).13</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>The article presents the results of an experimental study aimed at evaluating the effectiveness of an original program for harmonizing the psycho-emotional state of adolescent female handball players at the stage of preliminary basic training. The relevance of the research is due to the growing demands for emotional resilience in female athletes involved in team sports, where competitive performance largely depends on volitional regulation, anxiety levels, and the ability to manage emotions. The study involved 28 handball players from the main and reserve squads of the “Halychanka” club, who were divided into an experimental group (n=14) and a control group (n=14). The program for the experimental group combined traditional training loads with psychophysiological exercises, breathing relaxation techniques, visualization practices, cognitive-behavioral training, and individualized pedagogical support. The applied methods included the SAN questionnaire, the Spielberger–Khanin anxiety test, pedagogical observation, and statistical data analysis. The results showed statistically significant improvements in the experimental group: increases in well-being, activity, and mood indicators (up to 38%), as well as reductions in reactive and trait anxiety (by more than 8 points). The control group showed only minimal and statistically insignificant positive changes. The findings confirm the feasibility of implementing the proposed program in the training process of team sports athletes. Future research should focus on enhancing the program with consideration of individual psychophysiological profiles, testing it in various age groups, and exploring the long-term effects on athletes’ adaptive capacities.</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Avaliar a eficácia de um programa original de harmonização do estado psicoemocional de jogadoras adolescentes de handebol na etapa de preparação básica preliminar.</t>
         </is>
       </c>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>Experimental (grupo experimental e grupo controle; forma de alocação não informada).</t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>Dois grupos paralelos: o grupo experimental combinou cargas de treino tradicionais com exercícios psicofisiológicos, relaxamento respiratório, visualização, treino cognitivo-comportamental e apoio pedagógico individual; o grupo controle manteve o treino tradicional; momentos de medida e duração do programa não informados no resumo.</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Jogadoras adolescentes de handebol das equipes principal e reserva do clube Halychanka, na etapa de preparação básica preliminar; país não explícito no resumo.</t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>28 jogadoras: grupo experimental (n = 14) e grupo controle (n = 14); idade e perdas não informadas no resumo.</t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Ucrânia</t>
         </is>
       </c>
-      <c r="U35" s="3" t="inlineStr">
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>• Bem-estar, atividade e humor: questionário SAN
 • Ansiedade reativa (estado) e ansiedade traço: teste de Spielberger-Khanin</t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>• Questionário SAN (bem-estar, atividade, humor); número de itens, escala e confiabilidade não informados no resumo
 • Teste de ansiedade de Spielberger-Khanin (ansiedade reativa e traço)
 • Observação pedagógica</t>
         </is>
       </c>
-      <c r="W35" s="3" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>n.r. no resumo (presumivelmente antes e depois do programa).</t>
         </is>
       </c>
-      <c r="X35" s="3" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>Programa de harmonização do estado psicoemocional associado ao treino: exercícios psicofisiológicos, relaxamento respiratório, visualização, treino cognitivo-comportamental e apoio pedagógico individual; grupo experimental (n = 14) e controle (n = 14).</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>O grupo experimental teve melhoras estatisticamente significativas nos indicadores de bem-estar, atividade e humor (até 38%) e redução da ansiedade reativa e traço (mais de 8 pontos). O grupo controle teve apenas mudanças positivas mínimas e não significativas. O resumo não traz médias, DP nem valores de p.</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>Efeito ou associação</t>
         </is>
       </c>
-      <c r="AA35" s="3" t="n">
+      <c r="AA34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AB35" s="3" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>resumo</t>
         </is>
       </c>
-      <c r="AC35" s="3" t="inlineStr">
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>• Os autores propõem aperfeiçoar o programa com base em perfis psicofisiológicos individuais.
 • Os autores indicam a necessidade de testar o programa em outras faixas etárias.
@@ -6081,30 +5926,30 @@
 • Apenas o resumo está acessível: alocação, duração, idade e estatísticas não verificáveis.</t>
         </is>
       </c>
-      <c r="AD35" s="3" t="inlineStr">
+      <c r="AD34" s="2" t="inlineStr">
         <is>
           <t>O resumo relata melhora do bem-estar, da atividade e do humor e redução da ansiedade em jogadoras adolescentes submetidas a programa psicopedagógico integrado ao treino, sem mudança relevante no grupo controle. A ausência de estatísticas, de descrição da alocação e de detalhes do instrumento impede avaliar a robustez. A contribuição para o tema é indicar intervenções psicológicas no treino como via para modificar o humor em jovens handebolistas.</t>
         </is>
       </c>
-      <c r="AE35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36" ht="210" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="AE34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="210" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>H32</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>(BATALLA-GAVALDA et al., 2026)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>BATALLA-GAVALDA, A. et al. Ecological Validity of Maximal Exercise Tests to Simulate Competitive Demands in Amateur Female Handball. Acta Kinesiologica, p. 34-42, 2026. DOI: https://doi.org/10.51371/issn.1840-2976.651.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>• BATALLA-GAVALDA, Abraham
 • BELTRÁN-GARRIDO, Jose Vicente
@@ -6114,92 +5959,92 @@
 • DAZA-SOBRINO, Gabriel</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Ecological Validity of Maximal Exercise Tests to Simulate Competitive Demands in Amateur Female Handball</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Acta Kinesiologica</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>1840-3700, 1840-2976</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>não localizado</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>não localizado na fonte oficial</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.51371/issn.1840-2976.651</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Purpose: Laboratory tests are fundamental for assessing handball performance, but their ecological validity for amateur female players is unclear. This exploratory study compared physiological and perceptual responses between common maximal exercise tests and official match play to determine if they replicate competitive demands. Methods: Sixteen amateur female handball players completed three laboratory tests (Wingate, cycle ergometer, treadmill) and were monitored during ten official matches. The data collection included both physiological and psychological indicators: heart rate (HR), blood lactate concentration, rating of perceived exertion (RPE), perceived stress, and mood states. Results: Peak HR values recorded in the Wingate and Cycle ergometer were lower than those reached during actual competition (d = -.77 to -.75, P&lt; .05). In addition, compared with the Wingate and cycle ergometer tests, competitive matches required players to spend a significantly larger proportion of time with their HR exceeding 90% of its maximum. This contrast was less evident when compared with the treadmill test. A clear mismatch was observed between physiological and perceptual measures. Despite showing stronger physiological strain during matches -such as greater weight loss and higher pre-exercise lactate levels- players reported significantly lower RPE values than in the laboratory conditions (d = .27 to .36, P&lt; .05). Conclusions: None of the laboratory-based tests accurately reproduced the full demands of a handball match. Although the treadmill test elicited similar peak HR values, it failed to reflect the sport’s intermittent nature. The Wingate and cycle tests showed even greater discrepancies in cardiovascular intensity. These findings underline the importance of developing sport-specific or hybrid assessment protocols that integrate intermittent workloads and cognitive demands for a more valid evaluation of performance.</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>Determinar se os testes máximos de laboratório mais usados (Wingate, rampa em cicloergômetro e teste incremental em esteira) replicam as demandas fisiológicas e psicológicas de jogos oficiais em jogadoras amadoras de handebol.</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>Observacional exploratório com medidas repetidas (comparação intrassujeito entre condições).</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>Medidas repetidas em duas fases: pré-competitiva, com três testes de laboratório em duas sessões separadas por 48 h (Wingate e cicloergômetro na mesma sessão, com 30 min de intervalo; esteira na outra; ordem das sessões sorteada), e competitiva, com 10 jogos oficiais consecutivos; uma única medida de POMS e PSS para Wingate e cicloergômetro; modelos lineares mistos com intercepto aleatório por jogadora.</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Jogadoras amadoras de handebol do sexo feminino, adultas jovens, da categoria regional máxima da Catalunha (Liga Catalana Sénior Femenina); Espanha.</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>16 jogadoras (21,93 ± 3,25 anos; 1,66 ± 0,06 m; 64,36 ± 13,86 kg; gordura de 20,19 ± 3,37%; experiência de 10,44 ± 1,86 anos). Cálculo amostral: mínimo de 13, com 16 para prever perdas de 25%. Perdas não relatadas. Mesma amostra e mesmos dados de jogo de H31.</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T35" s="3" t="inlineStr">
         <is>
           <t>Espanha</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t>• Estados de humor (tensão-ansiedade, depressão-desânimo, raiva-hostilidade, vigor-atividade, fadiga-inércia, confusão-desorientação e PTH): POMS, versão espanhola de 58 itens
 • Estresse percebido: Perceived Stress Scale (PSS), versão espanhola de 14 itens
 • Percepção subjetiva de esforço: escalas de Borg 6-20 e CR-10</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t>• POMS em versão espanhola traduzida, 58 itens, escala de 0 a 4, dois itens invertidos; PTH com constante de 100; confiabilidade na amostra não relatada
 • Perceived Stress Scale (PSS), adaptação espanhola de 14 itens, aplicada antes de cada teste e jogo
@@ -6208,35 +6053,35 @@
 • Testes de laboratório: Wingate, rampa em cicloergômetro e teste incremental em esteira</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W35" s="3" t="inlineStr">
         <is>
           <t>O PSS foi aplicado antes de cada teste e jogo; o momento do POMS não é declarado explicitamente. Wingate e cicloergômetro tiveram uma única medida de PSS e POMS para os dois testes (valores idênticos). PSE (Borg 6-20 e CR-10) registrada 30 min após cada evento. Período de referência do POMS não relatado.</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t>não se aplica (comparação entre Wingate, rampa em cicloergômetro, teste em esteira e jogo oficial)</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>Médias (jogo; Wingate; cicloergômetro; esteira): tensão 10,17 ± 4,87; 10,81 ± 3,90; 10,81 ± 3,90; 11,00 ± 4,37. Depressão 7,74 ± 8,47; 8,13 ± 4,57; 8,13 ± 4,57; 7,06 ± 4,43. Raiva 8,03 ± 6,10; 8,19 ± 3,82; 8,19 ± 3,82; 8,50 ± 4,31. Vigor 10,78 ± 4,52; 11,88 ± 3,58; 11,88 ± 3,58; 13,31 ± 4,05 (esteira maior que jogo, d = 0,23, IC 95% 0,08 a 0,39, p = 0,003). Fadiga 6,02 ± 4,28; 7,69 ± 3,75; 7,69 ± 3,75; 7,25 ± 4,07 (Wingate e cicloergômetro maiores que jogo, d = 0,16, IC 95% 0,00 a 0,31, p = 0,046). Confusão 5,93 ± 3,61; 6,13 ± 3,07; 6,13 ± 3,07; 6,13 ± 3,03. PTH 127,12 ± 23,01; 129,06 ± 9,48; 129,06 ± 9,48; 126,63 ± 13,35. Estresse percebido 29,07 ± 8,28; 27,81 ± 5,89; 27,81 ± 5,89; 27,88 ± 5,54. Sem outras diferenças significativas no humor e no estresse. PSE (Borg 6-20) maior em todos os testes que no jogo (jogo 14,29 ± 3,23; Wingate 17,56 ± 1,26; cicloergômetro 17,44 ± 1,90; esteira 16,69 ± 0,95; d de 0,27 a 0,36; p &lt; 0,001).</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z35" s="3" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="n">
+      <c r="AA35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
+      <c r="AB35" s="3" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC36" s="2" t="inlineStr">
+      <c r="AC35" s="3" t="inlineStr">
         <is>
           <t>• Amostra pequena e cautela na generalização para outras modalidades, conforme os autores.
 • Testes aplicados uma única vez antes do período competitivo, limitação declarada pelos autores.
@@ -6244,34 +6089,34 @@
 • Momento de aplicação do POMS não declarado, o que impede atribuir as diferenças aos testes.</t>
         </is>
       </c>
-      <c r="AD36" s="2" t="inlineStr">
+      <c r="AD35" s="3" t="inlineStr">
         <is>
           <t>O estudo indica que testes máximos de laboratório pouco diferem dos jogos oficiais quanto ao humor, com apenas mais fadiga (Wingate e cicloergômetro) e mais vigor (esteira), em efeitos triviais a pequenos, ao passo que a percepção de esforço é maior nos testes. A robustez é limitada pela amostra de 16 jogadoras, coincidente com H31, pela duplicação da medida de Wingate e cicloergômetro e pelo momento do POMS não declarado. A contribuição para o tema é sugerir que o humor associado a testes de laboratório não reproduz de forma marcante o de competição em atletas amadoras.</t>
         </is>
       </c>
-      <c r="AE36" s="2" t="inlineStr">
+      <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>mesma amostra de H31</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="210" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="36" ht="210" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>H34</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>(RATZ-SULYOK et al., 2026b)</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>(RATZ-SULYOK et al., 2026)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>RATZ-SULYOK, F. Z. et al. Associations Between Endocrine Status and Stress, Mood and Psychosomatic Status in Elite Handball Players. Sports, v. 14, n. 7, e289, 2026. DOI: https://doi.org/10.3390/sports14070289.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>• RATZ-SULYOK, Fanny Zselyke
 • JANG-KAPUY, Csilla
@@ -6283,92 +6128,92 @@
 • SZABO, Tamas</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Associations Between Endocrine Status and Stress, Mood and Psychosomatic Status in Elite Handball Players</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2075-4663</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/sports14070289</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Purpose: The assessment of endocrine status in elite athletes is typically linked to training load and perceived stress; however, the relationship between hormonal parameters and psychosomatic and stress indicators remains insufficiently understood. This study aimed to investigate the associations between endocrine status and stress, mood, and psychosomatic status indicators in elite handball players. Methods: In a cross-sectional study, salivary cortisol (with no strict control over wake-up time), testosterone, and—in female athletes—17-β-estradiol concentrations were assessed in 584 elite handball players aged 14–35 years using ELISA. Psychological variables were evaluated using the Perceived Stress Scale (PSS), Profile of Mood States (POMS), and the Health Behavior in School-aged Children Symptom Checklist (HBSC-SCL). Associations were examined using non-parametric tests and general linear models adjusted for age. Results: Hormonal and psychological variables demonstrated significant age-related trends. No significant associations were observed between hormonal parameters and perceived stress or mood disturbance (values for the general linear model (GLM) were all p &gt; 0.05). In contrast, psychosomatic symptom severity was significantly associated with cortisol levels in male athletes (GLM, p &lt; 0.001) and testosterone levels in female athletes (GLM, p = 0.009). Multivariate analyses confirmed the relevance of psychosomatic symptoms and indicated interaction effects between stress-related factors. Conclusion: Psychosomatic symptoms were more closely associated with endocrine status than with perceived stress or mood disturbance in elite handball players. However, these associations were characterized by relatively small effect sizes, indicating that psychosomatic symptoms explain only a limited proportion of the variance in hormonal parameters. These findings suggest that psychosomatic indicators may provide a more sensitive reflection of physiological strain and support the use of integrated monitoring approaches combining endocrine and psychosomatic measures in elite sport. In practical terms, routine monitoring of psychosomatic symptoms alongside hormonal measures may help practitioners to identify early signs of physiological strain and support timely adjustments in training load and recovery strategies.</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Examinar as associações entre o estado endócrino salivar (cortisol, testosterona e, nas mulheres, 17-β-estradiol) e indicadores de estresse percebido, humor e sintomas psicossomáticos em jogadores de handebol de elite, sob a hipótese de que os sintomas psicossomáticos teriam associação mais forte com os hormônios que o estresse percebido ou o distúrbio de humor.</t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Observacional.</t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>Transversal, com avaliação única por atleta (saliva no dia dos exames antropométricos; questionários por entrevista em data não especificada em relação à coleta), análises não paramétricas e modelos lineares gerais univariados e multivariados ajustados pela idade, separados por sexo.</t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Jogadores de handebol de elite húngaros de ambos os sexos, de 14 a 35 anos, das seleções sub-17, sub-19, sub-21 e adulta e do programa de talentos sub-15, avaliados no centro de pesquisa da Federação Húngara de Handebol entre 2024 e 2025; Hungria.</t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>584 atletas (292 homens e 292 mulheres), de 14 a 35 anos; médias de idade apenas por faixa (por exemplo, adultos: homens 28,3 ± 4,3 anos; mulheres 25,9 ± 4,5 anos). POMS disponível para 276 atletas (109 homens e 167 mulheres), sem explicação das ausências; apenas 6 homens no grupo sub-19.</t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>Hungria</t>
         </is>
       </c>
-      <c r="U37" s="3" t="inlineStr">
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>• Distúrbio total de humor (PTH, a partir de tensão, depressão, raiva, fadiga, confusão e vigor): POMS de 65 itens
 • Estresse percebido: Perceived Stress Scale (PSS-14)
 • Sintomas psicossomáticos: Health Behavior in School-aged Children Symptom Checklist (HBSC-SCL) de 8 itens</t>
         </is>
       </c>
-      <c r="V37" s="3" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>• POMS de 65 itens, escala de 0 a 4, dois itens invertidos, referência à semana anterior, aplicado por entrevista pessoal estruturada; PTH sem constante, classificada pela distribuição da amostra em baixa, moderada e alta; idioma e confiabilidade não relatados
 • Perceived Stress Scale (PSS), 14 itens
@@ -6376,35 +6221,35 @@
 • Cortisol, testosterona e 17-β-estradiol salivares por ELISA (coleta entre 9h e 10h)</t>
         </is>
       </c>
-      <c r="W37" s="3" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>Saliva coletada entre 9h e 10h no dia dos exames antropométricos, com instrução para acordar entre 6h e 7h (não verificada). PSS, POMS e HBSC-SCL obtidos por entrevista pessoal estruturada, com data não especificada em relação à coleta de saliva, ao treino ou à competição. O POMS refere-se à semana anterior.</t>
         </is>
       </c>
-      <c r="X37" s="3" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>não se aplica</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>Medianas da PTH por faixa etária, homens: sub-15 8; sub-17 16; sub-19 1; sub-21 3; adultos -1. Mulheres: sub-15 15,5; sub-17 19; sub-19 25,5; sub-21 25; adultas -2,5; diferença entre faixas com p &lt; 0,001 (η² = 0,033 nos homens e 0,101 nas mulheres). Hormônios não diferiram entre categorias de PTH (testosterona: homens p = 0,338, mulheres p = 0,123; estradiol p = 0,691; cortisol: homens p = 0,860, mulheres p = 0,060). Modelo univariado ajustado pela idade, POMS: testosterona homens F = 1,549, p = 0,217; mulheres F = 1,266, p = 0,285; estradiol F = 0,120, p = 0,887; cortisol homens F = 1,773, p = 0,175; mulheres F = 0,633, p = 0,533. Modelo multivariado: POMS homens F = 1,496, p = 0,205; mulheres F = 1,448, p = 0,196; interação PSS × POMS nos homens F = 2,820, p = 0,026, η² parcial = 0,055. HBSC-SCL associou-se ao cortisol nos homens (F = 12,43; p &lt; 0,001; η² parcial = 0,043) e à testosterona nas mulheres (F = 4,78; p = 0,009; η² parcial = 0,095). PSS, POMS e HBSC-SCL diminuíram com a idade, conforme os autores, embora a mediana da PTH feminina suba de sub-15 a sub-19.</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
-      <c r="AA37" s="3" t="n">
+      <c r="AA36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AB37" s="3" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>texto completo</t>
         </is>
       </c>
-      <c r="AC37" s="3" t="inlineStr">
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>• Delineamento transversal sem inferência causal e efeitos pequenos, de relevância prática limitada, conforme os autores.
 • Ausência de controle rigoroso do horário de despertar e de fatores prévios à coleta, e ausência de medidas de carga de treino, sono e recuperação, declaradas pelos autores.
@@ -6412,346 +6257,15 @@
 • Data da entrevista psicológica em relação à coleta de saliva e ao calendário competitivo não informada.</t>
         </is>
       </c>
-      <c r="AD37" s="3" t="inlineStr">
+      <c r="AD36" s="2" t="inlineStr">
         <is>
           <t>Em grande amostra de atletas de elite, o distúrbio de humor não se associou aos hormônios salivares de repouso, ao passo que os sintomas psicossomáticos mostraram associações pequenas com cortisol (homens) e testosterona (mulheres). A robustez é reduzida pela disponibilidade do POMS em apenas 276 de 584 atletas, por pontos de corte derivados da própria amostra e por η² parciais incoerentes com alguns F relatados. A contribuição para o tema é descrever a PTH de handebolistas de elite por faixa etária e sexo e sugerir que o humor global, isolado, é marcador pouco sensível do estado endócrino.</t>
         </is>
       </c>
-      <c r="AE37" s="3" t="inlineStr">
-        <is>
-          <t>amostra também descrita em N9</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="210" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>N6</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>(BUGTEN et al., 2026)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>BUGTEN, J. B. et al. Youth players basic need satisfaction, enjoyment and pleasure within daily team sport training sessions, and the relationships with physical load engagement: an intensive within-person longitudinal study. Research Square, 2026. Preprint. DOI: https://doi.org/10.21203/rs.3.rs-8338987/v1.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>• BUGTEN, Jesper Barth
-• HAUGEN, Tommy
-• SPENCER, Matt
-• IVARSSON, Andreas
-• BYRKJEDAL, Per Thomas
-• STENLING, Andreas
-• SOLSTAD, Bård Erlend</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Youth Players Basic Need Satisfaction, Enjoyment and Pleasure within daily team sport training sessions, and the relationships with Physical Load Engagement: An intensive within-person longitudinal study</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Research Square</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica (preprint)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.21203/rs.3.rs-8338987/v1</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Youth team-sport training sessions provide repeated opportunities for skill development, yet little is known about how athletes’ momentary psychological experiences relate to their physical engagement in training. Fifty adolescent female handball players (M = 14.57, SD = 1.03) completed brief questionnaires before and after 11–12 consecutive team training sessions, while physical load (PlayerLoad™) and high-intensity events (&gt; 1.5 m/s²) were recorded via inertial measurement units during training. Bayesian within-person analysis revealed temporal stability in basic need satisfaction, sport enjoyment, and feelings of pleasure before and after training. Before and after training, basic needs satisfaction was associated with sport enjoyment and pleasure. Pleasure before training was associated with physical load during training, which was further associated with pleasure after training. This highlights that youth athletes’ basic need satisfaction and affective experiences are intertwined with their physical engagement in training, underscoring the importance of creating need-supportive training environments that foster both positive affect and meaningful behavioral involvement for athlete development in youth sport.</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Examinar as associações entre satisfação das necessidades psicológicas básicas, prazer esportivo e sensação de prazer antes e depois de treinos de handebol de base, e destas variáveis com a carga física e os eventos de alta intensidade durante o treino.</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Observacional.</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>Longitudinal intensivo intrapessoal, com 11 a 12 sessões consecutivas de treino por equipe em quatro semanas; questionário cerca de 15 min antes e até 15 min depois de cada sessão e carga física registrada de forma contínua durante o treino; modelagem de equações estruturais multinível bayesiana.</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Jogadoras de handebol de base do sexo feminino, de 14 a 16 anos, de duas equipes norueguesas (sub-14 e sub-16), em competição local, com cerca de três treinos de 90 min por semana; Noruega.</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>50 jogadoras (14,57 ± 1,03 anos); número de observações válidas, adesão e perdas não relatados. A mesma amostra foi usada em outros manuscritos dos autores (H33 e Bugten et al., 2025b; 2025c).</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>• Sensação de prazer (afeto central, valência): Feeling Scale, item único de -5 a +5
-• Prazer esportivo: item do Sport Commitment Questionnaire (SCQ), escala de 1 a 5
-• Satisfação das necessidades psicológicas básicas (autonomia, competência e relação): PNSSS de 9 itens</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>• Feeling Scale (Hardy e Rejeski, 1989), item único "How do you feel right now?", escala bipolar de 11 pontos de -5 (muito mal) a +5 (muito bem), traduzida para o norueguês e adaptada
-• Item do Sport Commitment Questionnaire para prazer esportivo (1 a 5)
-• PNSSS, 9 itens (autonomia, competência e relação), ômega de 0,76 a 0,89
-• Unidades de medida inercial Catapult OptimEye S5 (100 Hz) para PlayerLoad e eventos de alta intensidade (&gt; 1,5 m/s²)</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>Questionário digital cerca de 15 min antes do início de cada sessão e até 15 min depois do fim, no local de treino e sob supervisão; carga física registrada continuamente por IMU (Catapult OptimEye S5, 100 Hz).</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t>Sensação de prazer 3,03 ± 1,14 (ICC = 0,29); prazer esportivo 4,34 ± 0,96 (ICC = 0,63). Prazer antes predisse prazer depois (β = 0,55; IC95% 0,47 a 0,63). Prazer antes associou-se à carga física (PlayerLoad) no treino (β = 0,14 a 0,17; IC95% 0,03 a 0,28), e a carga associou-se ao prazer depois (β = 0,09; IC95% 0,01 a 0,17). Prazer antes predisse prazer esportivo depois (β = 0,13 a 0,15; IC95% 0,04 a 0,24). Competência depois (β = 0,23; IC95% 0,13 a 0,31), relação depois (β = 0,15; IC95% 0,06 a 0,24) e autonomia depois (β = 0,11; IC95% 0,01 a 0,20) associaram-se ao prazer depois; relação antes (r = 0,43), competência antes (r = 0,37) e autonomia antes (r = 0,36) associaram-se ao prazer antes. Satisfação das necessidades estável antes e depois (β de 0,63 a 0,68). Eventos de alta intensidade não se associaram a nenhuma variável psicológica.</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>Efeito ou associação</t>
-        </is>
-      </c>
-      <c r="AA38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>texto completo</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>• Delineamento observacional sem inferência causal; os autores recomendam estudos experimentais ou de microintervenção.
-• PlayerLoad e eventos de alta intensidade captam apenas parte do engajamento físico, e o limiar de 1,5 m/s² pode ser baixo, conforme os autores.
-• Clima motivacional do treinador e interações com pares não medidos, declarados pelos autores.
-• Amostra de adolescentes norueguesas com generalização limitada; preprint sem revisão por pares e dados ausentes não relatados.</t>
-        </is>
-      </c>
-      <c r="AD38" s="2" t="inlineStr">
-        <is>
-          <t>Em 50 jovens handebolistas acompanhadas em cerca de 12 treinos, o prazer antes do treino associou-se a maior carga física, que se associou a maior prazer depois, e a satisfação das necessidades básicas acompanhou o afeto positivo. Os coeficientes são pequenos, com limites inferiores próximos de zero, e o texto é preprint sem revisão por pares, com amostra compartilhada com outros artigos. A contribuição para o tema é inédita ao tratar o afeto como entrada dinâmica e não só como produto do engajamento físico no treino de handebol.</t>
-        </is>
-      </c>
-      <c r="AE38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39" ht="210" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>N9</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>(RATZ-SULYOK et al., 2026a)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>RATZ-SULYOK, F. Z. et al. Stress and sex hormone changes of young elite handball players in relation to their mood profiles. Anthropologiai Közlemények, n. 67, supl., p. 108, 2026. Resumo. DOI: https://doi.org/10.20330/anthropkozl.2026.67s.108.</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>• RATZ-SULYOK, Fanny Zselyke
-• JANG-KAPUY, Csilla
-• BAKONYI, Peter
-• BERES, Bettina
-• DOBRONYI, Tamas
-• SIMON, Gergo
-• ZSAKAI, Annamaria
-• SZABO, Tamas</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Stress and sex hormone changes of young elite handball players in relation to their mood profiles</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Anthropologiai Közlemények</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>2560-0753, 0003-5440</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>não localizado</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>não localizado</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.20330/anthropkozl.2026.67s.108</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Background: Excessive training-induced stress in athletes is theorised to cause maladaptation in athletes, when there is an imbalance in training and recovery, which can later lead to overtraining syndrome (OTS). OTS detection is prominently based on the change of testosterone and cortisol levels due to maximal exertion, alongside mood profiling. Objective: To study the relationship between mood profile, stress state, endocrine status and response to physical exertion in youth handball players. The analysis is part of a large study to develop a new screening method for overtraining status in athletes. Subjects and methods: 584 elite Hungarian handball players (14–35 ys) were examined in the Sport Sciences and Diagnostic Research Centre of the Hungarian Handball Federation between 2023 and 2025. Saliva samples were collected in resting state and after vital maximum exertion to measure the concentration of testosterone and cortisol, and 17-β-oestradiol hormone levels. Hormone levels were estimated by ELISA method. Subjective stress state of the athletes was surveyed via Profile of Mood States questionnaire. Results: The athlete references of resting levels of sex hormones, as well as the change in the ratio of sex hormone and cortisol hormone levels were constructed for athletes. Sex hormone levels showed deviations from the non-athlete references in both sexes: the resting testosterone level of male athletes was higher, while 17-β-oestradiol level of female athletes was lower than non-athletes’ level in their age-groups. Physical exertion caused all three hormone levels to change significantly in both sexes. The testosterone/cortisol ratio change showed relation to the mood profile of the athletes. Conclusions: New indices based on sex hormone and cortisol levels are under construction for the screening of overtraining in athletes. Our further aim is to study fatigue, inflammatory and immune biomarkers beside the studied hormone levels to analyse their relations with injury risk in elite athletes.</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>Estudar a relação entre perfil de humor, estado de estresse, estado endócrino e resposta ao esforço físico em handebolistas jovens, como parte de estudo maior para o desenvolvimento de novo método de triagem do estado de overtraining em atletas.</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>Observacional (resumo de congresso).</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>Transversal, com coleta de saliva em repouso e após esforço máximo e aplicação do POMS em momento não informado.</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>Handebolistas húngaros de elite de 14 a 35 anos avaliados no Sport Sciences and Diagnostic Research Centre da Federação Húngara de Handebol entre 2023 e 2025; Hungria.</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>584 atletas de 14 a 35 anos; distribuição por sexo, médias de idade e perdas não informadas no resumo. Mesma amostra de H34.</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>Hungria</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>• Perfil de humor e estado subjetivo de estresse: Profile of Mood States (POMS), versão não informada no resumo</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>• Profile of Mood States (POMS); versão, itens e confiabilidade não informados no resumo (o artigo H34, da mesma amostra, informa POMS de 65 itens)
-• Testosterona, cortisol e 17-β-estradiol salivares por ELISA, em repouso e após esforço máximo</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>Saliva coletada em repouso e após esforço máximo (testosterona, cortisol e 17-β-estradiol por ELISA); POMS aplicado em momento n.r.</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>A variação da razão testosterona/cortisol com o esforço mostrou relação com o perfil de humor dos atletas; magnitude, direção e estatísticas não informadas. Testosterona de repouso maior nos homens atletas e 17-β-estradiol menor nas mulheres atletas que nos não atletas de mesma faixa etária; o esforço físico alterou de forma significativa os três hormônios nos dois sexos.</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>Misto</t>
-        </is>
-      </c>
-      <c r="AA39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB39" s="3" t="inlineStr">
-        <is>
-          <t>resumo</t>
-        </is>
-      </c>
-      <c r="AC39" s="3" t="inlineStr">
-        <is>
-          <t>• Os autores pretendem estudar biomarcadores de fadiga, inflamação e imunidade junto aos hormônios.
-• A relação desses marcadores com o risco de lesão em atletas de elite permanece não investigada, conforme os autores.
-• Os índices hormonais para triagem do overtraining ainda estão em construção.
-• Resumo sem estatísticas do humor e sem direção da relação entre razão testosterona/cortisol e perfil de humor.</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>O resumo de congresso relata, em 584 handebolistas húngaros de elite, relação entre a variação da razão testosterona/cortisol induzida por esforço máximo e o perfil de humor. Sem dados numéricos, não é possível avaliar a robustez, e a amostra coincide com a de H34, que não encontrou associação entre PTH e hormônios de repouso. A contribuição para o tema é sugerir que a resposta hormonal ao esforço, e não o nível de repouso, pode se relacionar ao humor.</t>
-        </is>
-      </c>
-      <c r="AE39" s="3" t="inlineStr">
-        <is>
-          <t>mesma amostra de H34</t>
-        </is>
-      </c>
+      <c r="AE36" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE39"/>
+  <autoFilter ref="A1:AE36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6762,7 +6276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6892,346 +6406,310 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>(BUGTEN et al., 2026)</t>
+          <t>(DIACHENKO; TYSHCHENKO, 2025)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>BUGTEN, J. B. et al. Youth players basic need satisfaction, enjoyment and pleasure within daily team sport training sessions, and the relationships with physical load engagement: an intensive within-person longitudinal study. Research Square, 2026. Preprint. DOI: https://doi.org/10.21203/rs.3.rs-8338987/v1.</t>
+          <t>DIACHENKO, M.; TYSHCHENKO, V. Psycho-emotional regulation of female handball players during training. Scientific Journal of National Pedagogical Dragomanov University. Series 15: Scientific and Pedagogical Problems of Physical Culture (Physical Culture and Sports), n. 5K(191), p. 66-70, 2025. DOI: https://doi.org/10.31392/udu-nc.series15.2025.05k(191).13.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>(DIACHENKO; TYSHCHENKO, 2025)</t>
+          <t>(DURAI; ATHISAYARAJ, 2018)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>DIACHENKO, M.; TYSHCHENKO, V. Psycho-emotional regulation of female handball players during training. Scientific Journal of National Pedagogical Dragomanov University. Series 15: Scientific and Pedagogical Problems of Physical Culture (Physical Culture and Sports), n. 5K(191), p. 66-70, 2025. DOI: https://doi.org/10.31392/udu-nc.series15.2025.05k(191).13.</t>
+          <t>DURAI, C.; ATHISAYARAJ, S. Comparison of mood states between handball and volleyball players. International Journal of Physiology, Nutrition and Physical Education, v. 3, n. 2, p. 43-44, 2018.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>(DURAI; ATHISAYARAJ, 2018)</t>
+          <t>(ESSID et al., 2022)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>DURAI, C.; ATHISAYARAJ, S. Comparison of mood states between handball and volleyball players. International Journal of Physiology, Nutrition and Physical Education, v. 3, n. 2, p. 43-44, 2018.</t>
+          <t>ESSID, S. et al. Time-of-day effects in physical performances and psychological responses in young elite male handball players. Biological Rhythm Research, v. 53, n. 8, p. 1261-1272, 2022. DOI: https://doi.org/10.1080/09291016.2021.1922212.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>(ESSID et al., 2022)</t>
+          <t>(FARZANEGI et al., [2008?])</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ESSID, S. et al. Time-of-day effects in physical performances and psychological responses in young elite male handball players. Biological Rhythm Research, v. 53, n. 8, p. 1261-1272, 2022. DOI: https://doi.org/10.1080/09291016.2021.1922212.</t>
+          <t>FARZANEGI, P. et al. The effect of winning/losing on profiles of mood states and salivary cortisol concentration in female handball players. Tehran: Islamic Azad University, [2008?]. Disponível em: https://sanad.iau.ir/en/Article/889921. Acesso em: 21 out. 2026.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>(FARZANEGI et al., [2008?])</t>
+          <t>(GARCÍA-HERRERO et al., 2022)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>FARZANEGI, P. et al. The effect of winning/losing on profiles of mood states and salivary cortisol concentration in female handball players. Tehran: Islamic Azad University, [2008?]. Disponível em: https://sanad.iau.ir/en/Article/889921. Acesso em: 21 out. 2026.</t>
+          <t>GARCÍA-HERRERO, J. A. et al. Analysis of the Relationship between Satisfaction with the Coach and the Effect of Comparative Social Feedback in Elite Female Handball Players. International Journal of Environmental Research and Public Health, v. 19, n. 13, e7680, 2022. DOI: https://doi.org/10.3390/ijerph19137680.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>(GARCÍA-HERRERO et al., 2022)</t>
+          <t>(GHAZEL et al., 2022)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>GARCÍA-HERRERO, J. A. et al. Analysis of the Relationship between Satisfaction with the Coach and the Effect of Comparative Social Feedback in Elite Female Handball Players. International Journal of Environmental Research and Public Health, v. 19, n. 13, e7680, 2022. DOI: https://doi.org/10.3390/ijerph19137680.</t>
+          <t>GHAZEL, N. et al. The effect of music on short-term exercise performance during the different menstrual cycle phases in female handball players. Research in Sports Medicine, v. 30, n. 1, p. 50-60, 2022. DOI: https://doi.org/10.1080/15438627.2020.1860045.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>(GHAZEL et al., 2022)</t>
+          <t>(IVANOVIĆ; IVANOVIĆ, 2023)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>GHAZEL, N. et al. The effect of music on short-term exercise performance during the different menstrual cycle phases in female handball players. Research in Sports Medicine, v. 30, n. 1, p. 50-60, 2022. DOI: https://doi.org/10.1080/15438627.2020.1860045.</t>
+          <t>IVANOVIĆ, M.; IVANOVIĆ, U. Influence of health status and loneliness on satisfaction with life, emotional dimensions, and distress in junior handball players. Exercise and Quality of Life, v. 15, n. 1, p. 27-35, 2023. DOI: https://doi.org/10.31382/eqol.230604.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>(IVANOVIĆ; IVANOVIĆ, 2023)</t>
+          <t>(KHAZDOZI; BAHARI; ASHAYERI, 2017)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>IVANOVIĆ, M.; IVANOVIĆ, U. Influence of health status and loneliness on satisfaction with life, emotional dimensions, and distress in junior handball players. Exercise and Quality of Life, v. 15, n. 1, p. 27-35, 2023. DOI: https://doi.org/10.31382/eqol.230604.</t>
+          <t>KHAZDOZI, G.; BAHARI, S. M.; ASHAYERI, H. Effects of Warming up with Music on Moods and Training Motivation among Athletes. Journal of History Culture and Art Research, v. 6, n. 1, e169, 2017. DOI: https://doi.org/10.7596/taksad.v6i1.713.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>(KHAZDOZI; BAHARI; ASHAYERI, 2017)</t>
+          <t>(LAGNER et al., 2015)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>KHAZDOZI, G.; BAHARI, S. M.; ASHAYERI, H. Effects of Warming up with Music on Moods and Training Motivation among Athletes. Journal of History Culture and Art Research, v. 6, n. 1, e169, 2017. DOI: https://doi.org/10.7596/taksad.v6i1.713.</t>
+          <t>LAGNER, P. et al. Mood effects on memory and executive control in a real-life situation. Cognition and Emotion, v. 29, n. 6, p. 1107-1116, 2015. DOI: https://doi.org/10.1080/02699931.2014.962486.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>(LAGNER et al., 2015)</t>
+          <t>(LISENCHUK et al., 2019)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>LAGNER, P. et al. Mood effects on memory and executive control in a real-life situation. Cognition and Emotion, v. 29, n. 6, p. 1107-1116, 2015. DOI: https://doi.org/10.1080/02699931.2014.962486.</t>
+          <t>LISENCHUK, G. et al. Analysis of psychological state of qualified female handball players depending on the phase of the ovarian-menstrual cycle. Journal of Physical Education and Sport, v. 19, supl. 3, art. 115, p. 808-812, 2019. DOI: https://doi.org/10.7752/jpes.2019.s3115.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>(LISENCHUK et al., 2019)</t>
+          <t>(LUJIC; PRSKALO; BRATKO, 2023)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>LISENCHUK, G. et al. Analysis of psychological state of qualified female handball players depending on the phase of the ovarian-menstrual cycle. Journal of Physical Education and Sport, v. 19, supl. 3, art. 115, p. 808-812, 2019. DOI: https://doi.org/10.7752/jpes.2019.s3115.</t>
+          <t>LUJIC, M.; PRSKALO, I.; BRATKO, D. difference in well-being between handball players and ones not physically active. Scientific Journal of Sport and Performance, v. 2, n. 2, p. 144-150, 2023. DOI: https://doi.org/10.55860/fhsl7752.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>(LUJIC; PRSKALO; BRATKO, 2023)</t>
+          <t>(MIRALLES-AMORÓS et al., 2023)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>LUJIC, M.; PRSKALO, I.; BRATKO, D. difference in well-being between handball players and ones not physically active. Scientific Journal of Sport and Performance, v. 2, n. 2, p. 144-150, 2023. DOI: https://doi.org/10.55860/fhsl7752.</t>
+          <t>MIRALLES-AMORÓS, L. et al. Study of Different Personalised Dietary Plans on Eating Behaviour, Body Image and Mood in Young Female Professional Handball Players: A Randomised Controlled Trial. Children, v. 10, n. 2, e259, 2023. DOI: https://doi.org/10.3390/children10020259.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>(MIRALLES-AMORÓS et al., 2023)</t>
+          <t>(MON-LÓPEZ et al., 2020)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>MIRALLES-AMORÓS, L. et al. Study of Different Personalised Dietary Plans on Eating Behaviour, Body Image and Mood in Young Female Professional Handball Players: A Randomised Controlled Trial. Children, v. 10, n. 2, e259, 2023. DOI: https://doi.org/10.3390/children10020259.</t>
+          <t>MON-LÓPEZ, D. et al. The Impact of Covid-19 and the Effect of Psychological Factors on Training Conditions of Handball Players. International Journal of Environmental Research and Public Health, v. 17, n. 18, e6471, 2020. DOI: https://doi.org/10.3390/ijerph17186471.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>(MON-LÓPEZ et al., 2020)</t>
+          <t>(MONTES; GOMES, 2014)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MON-LÓPEZ, D. et al. The Impact of Covid-19 and the Effect of Psychological Factors on Training Conditions of Handball Players. International Journal of Environmental Research and Public Health, v. 17, n. 18, e6471, 2020. DOI: https://doi.org/10.3390/ijerph17186471.</t>
+          <t>MONTES, F. A.; GOMES, S. C. Correlação entre resistência anaeróbia e estados de humor ao longo de uma temporada na modalidade handebol. UNOPAR Científica Ciências Biológicas e da Saúde, v. 16, n. 2, p. 83-86, 2014.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>(MONTES; GOMES, 2014)</t>
+          <t>(MORENAS-AGUILAR et al., 2023)</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>MONTES, F. A.; GOMES, S. C. Correlação entre resistência anaeróbia e estados de humor ao longo de uma temporada na modalidade handebol. UNOPAR Científica Ciências Biológicas e da Saúde, v. 16, n. 2, p. 83-86, 2014.</t>
+          <t>MORENAS-AGUILAR, M. et al. The menstrual cycle does not influence vertical jump performance or throwing velocity in amateur team handball players. Science &amp;amp; Sports, v. 38, n. 2, p. 211-215, 2023. DOI: https://doi.org/10.1016/j.scispo.2022.02.008.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>(MORENAS-AGUILAR et al., 2023)</t>
+          <t>(OBREGÓN SIBÓN et al., 2017)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>MORENAS-AGUILAR, M. et al. The menstrual cycle does not influence vertical jump performance or throwing velocity in amateur team handball players. Science &amp;amp; Sports, v. 38, n. 2, p. 211-215, 2023. DOI: https://doi.org/10.1016/j.scispo.2022.02.008.</t>
+          <t>OBREGÓN SIBÓN, I. et al. Cambios postest en el umbral mecánico nociceptivo de la musculatura del hombro y en el estado de ánimo en jugadores de balonmano. Cuestiones de Fisioterapia, v. 46, n. 3, p. 183-191, 2017. Disponível em: https://dialnet.unirioja.es/servlet/articulo?codigo=6263341. Acesso em: 21 out. 2026.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>(NUGRAHA; WIBOWO; FIRMANSYAH, 2020)</t>
+          <t>(PADILHAS et al., 2018)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>NUGRAHA, E.; WIBOWO, R.; FIRMANSYAH, H. Mood states and game performance in invasion game activities: a correlation study among elementary school students. *In*: INTERNATIONAL CONFERENCE ON SPORT SCIENCE, HEALTH, AND PHYSICAL EDUCATION, 4., 2019, Bandung. Proceedings [...]. Paris: Atlantis Press, 2020. p. 95-98. DOI: https://doi.org/10.2991/ahsr.k.200214.027.</t>
+          <t>PADILHAS, O. P. et al. Inter season physiological control of the brazilian beach handball team. Revista Brasileira de Medicina do Esporte, v. 24, n. 6, p. 436-439, 2018. DOI: https://doi.org/10.1590/1517-869220182406153471.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>(OBREGÓN SIBÓN et al., 2017)</t>
+          <t>(PEREIRA et al., 2014)</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>OBREGÓN SIBÓN, I. et al. Cambios postest en el umbral mecánico nociceptivo de la musculatura del hombro y en el estado de ánimo en jugadores de balonmano. Cuestiones de Fisioterapia, v. 46, n. 3, p. 183-191, 2017. Disponível em: https://dialnet.unirioja.es/servlet/articulo?codigo=6263341. Acesso em: 21 out. 2026.</t>
+          <t>PEREIRA, R. et al. Avaliação do Estado Fisiológico de Escolares Atletas. Revista Brasileira de Ciências da Saúde, v. 18, n. S4, p. 75-82, 2014. DOI: https://doi.org/10.4034/RBCS.2014.18.S4.10.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>(PADILHAS et al., 2018)</t>
+          <t>(RATZ-SULYOK et al., 2026)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>PADILHAS, O. P. et al. Inter season physiological control of the brazilian beach handball team. Revista Brasileira de Medicina do Esporte, v. 24, n. 6, p. 436-439, 2018. DOI: https://doi.org/10.1590/1517-869220182406153471.</t>
+          <t>RATZ-SULYOK, F. Z. et al. Associations Between Endocrine Status and Stress, Mood and Psychosomatic Status in Elite Handball Players. Sports, v. 14, n. 7, e289, 2026. DOI: https://doi.org/10.3390/sports14070289.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>(PEREIRA et al., 2014)</t>
+          <t>(REIGAL et al., 2020)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>PEREIRA, R. et al. Avaliação do Estado Fisiológico de Escolares Atletas. Revista Brasileira de Ciências da Saúde, v. 18, n. S4, p. 75-82, 2014. DOI: https://doi.org/10.4034/RBCS.2014.18.S4.10.</t>
+          <t>REIGAL, R. E. et al. Psychological Profile, Competitive Anxiety, Moods and Self-Efficacy in Beach Handball Players. International Journal of Environmental Research and Public Health, v. 17, n. 1, e241, 2020. DOI: https://doi.org/10.3390/ijerph17010241.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>(RATZ-SULYOK et al., 2026b)</t>
+          <t>(ROCHA; LOPES; MORAES, 2010)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>RATZ-SULYOK, F. Z. et al. Associations Between Endocrine Status and Stress, Mood and Psychosomatic Status in Elite Handball Players. Sports, v. 14, n. 7, e289, 2026. DOI: https://doi.org/10.3390/sports14070289.</t>
+          <t>ROCHA, P. G. M. D.; LOPES, J. L.; MORAES, S. M. F. D. Efeito da alteração ambiental sobre componentes psicológicos e parâmetros fisiológicos durante corrida em atletas. Psicologia: Teoria e Pesquisa, v. 26, n. 2, p. 381-386, 2010. DOI: https://doi.org/10.1590/S0102-37722010000200020.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>(RATZ-SULYOK et al., 2026a)</t>
+          <t>(SAHLI et al., 2024)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>RATZ-SULYOK, F. Z. et al. Stress and sex hormone changes of young elite handball players in relation to their mood profiles. Anthropologiai Közlemények, n. 67, supl., p. 108, 2026. Resumo. DOI: https://doi.org/10.20330/anthropkozl.2026.67s.108.</t>
+          <t>SAHLI, F. et al. Enhancing Skills, Mood, and Performance in Overweight Handball Players: Exploring Individual vs. Collective Verbal Encouragement Strategies. Children, v. 11, n. 4, e432, 2024. DOI: https://doi.org/10.3390/children11040432.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>(REIGAL et al., 2020)</t>
+          <t>(SAHLI et al., 2022)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>REIGAL, R. E. et al. Psychological Profile, Competitive Anxiety, Moods and Self-Efficacy in Beach Handball Players. International Journal of Environmental Research and Public Health, v. 17, n. 1, e241, 2020. DOI: https://doi.org/10.3390/ijerph17010241.</t>
+          <t>SAHLI, F. et al. The Effects of Combined Verbal Encouragement and Technical Instruction on Technical Skills and Psychophysiological Responses During Small-Sided Handball Games Exercise in Physical Education. Frontiers in Psychology, v. 13, e902088, 2022. DOI: https://doi.org/10.3389/fpsyg.2022.902088.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>(ROCHA; LOPES; MORAES, 2010)</t>
+          <t>(SCHIAVINI; ARENA, 2010)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>ROCHA, P. G. M. D.; LOPES, J. L.; MORAES, S. M. F. D. Efeito da alteração ambiental sobre componentes psicológicos e parâmetros fisiológicos durante corrida em atletas. Psicologia: Teoria e Pesquisa, v. 26, n. 2, p. 381-386, 2010. DOI: https://doi.org/10.1590/S0102-37722010000200020.</t>
+          <t>SCHIAVINI, C.; ARENA, R. Influence of the semi-final stage on mood in female handball athletes at Unisinos Championship 2008. FIEP Bulletin, v. 80, edição especial, p. 625-628, 2010.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>(SAHLI et al., 2024)</t>
+          <t>(SOTO; GARCÍA-HERRERO; CARCEDO, 2020)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>SAHLI, F. et al. Enhancing Skills, Mood, and Performance in Overweight Handball Players: Exploring Individual vs. Collective Verbal Encouragement Strategies. Children, v. 11, n. 4, e432, 2024. DOI: https://doi.org/10.3390/children11040432.</t>
+          <t>SOTO, D.; GARCÍA-HERRERO, J. A.; CARCEDO, R. J. Well-Being and Throwing Speed of Women Handball Players Affected by Feedback. International Journal of Environmental Research and Public Health, v. 17, n. 17, e6064, 2020. DOI: https://doi.org/10.3390/ijerph17176064.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>(SAHLI et al., 2022)</t>
+          <t>(ZURITA ORTEGA et al., 2014)</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>SAHLI, F. et al. The Effects of Combined Verbal Encouragement and Technical Instruction on Technical Skills and Psychophysiological Responses During Small-Sided Handball Games Exercise in Physical Education. Frontiers in Psychology, v. 13, e902088, 2022. DOI: https://doi.org/10.3389/fpsyg.2022.902088.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>(SCHIAVINI; ARENA, 2010)</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>SCHIAVINI, C.; ARENA, R. Influence of the semi-final stage on mood in female handball athletes at Unisinos Championship 2008. FIEP Bulletin, v. 80, edição especial, p. 625-628, 2010.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>(SOTO; GARCÍA-HERRERO; CARCEDO, 2020)</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>SOTO, D.; GARCÍA-HERRERO, J. A.; CARCEDO, R. J. Well-Being and Throwing Speed of Women Handball Players Affected by Feedback. International Journal of Environmental Research and Public Health, v. 17, n. 17, e6064, 2020. DOI: https://doi.org/10.3390/ijerph17176064.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>(ZURITA ORTEGA et al., 2014)</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>ZURITA ORTEGA, F. et al. Aspectos psicosomáticos implicados en las lesiones deportivas. Cuadernos de Psicología del Deporte, v. 14, n. 2, p. 81-88, 2014. DOI: https://doi.org/10.4321/s1578-84232014000200009.</t>
         </is>
@@ -7248,7 +6726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8403,60 +7881,64 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>U107</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Proceedings of the 4th International Conference on Sport Science, Health, and Physical Education (ICSSHPE 2019)</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
+          <t>International Journal of Environmental Research and Public Health</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>1660-4601</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>todas as 38 áreas em que o periódico consta (estrato único); área-mãe: SAÚDE COLETIVA</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>não se aplica</t>
+          <t>todas as 46 áreas em que o periódico consta (estrato único); área-mãe: SAÚDE COLETIVA</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>não consultado (sem periódico/ISSN aplicável)</t>
+          <t>Plataforma Sucupira, consulta pública Qualis Periódicos: https://sucupira-legado.capes.gov.br/sucupira/public/consultas/coleta/veiculoPublicacaoQualis/listaConsultaGeralPeriodicos.jsf</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Anais de evento (Atlantis Press, Advances in Health Sciences Research); anais não recebem Qualis Periódicos.</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1660-4601 (INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH). 2021-2024: encontrado por 1660-4601 (INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -8513,47 +7995,47 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>H23</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>International Journal of Environmental Research and Public Health</t>
+          <t>Research in Sports Medicine</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1660-4601</t>
+          <t>1543-8627, 1543-8635</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>todas as 4 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>todas as 38 áreas em que o periódico consta (estrato único); área-mãe: SAÚDE COLETIVA</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>todas as 46 áreas em que o periódico consta (estrato único); área-mãe: SAÚDE COLETIVA</t>
+          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -8563,54 +8045,54 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1660-4601 (INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH). 2021-2024: encontrado por 1660-4601 (INTERNATIONAL JOURNAL OF ENVIRONMENTAL RESEARCH AND PUBLIC HEALTH).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1543-8627 (RESEARCH IN SPORTS MEDICINE (PRINT)); sem registro para 1543-8635. 2021-2024: encontrado por 1543-8627 (RESEARCH IN SPORTS MEDICINE (PRINT)); sem registro para 1543-8635.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>H24</t>
+          <t>H25</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Research in Sports Medicine</t>
+          <t>Frontiers in Psychology</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1543-8627, 1543-8635</t>
+          <t>1664-1078</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>todas as 29 áreas em que o periódico consta (estrato único); área-mãe: PSICOLOGIA</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>todas as 4 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+          <t>todas as 35 áreas em que o periódico consta (estrato único); área-mãe: PSICOLOGIA</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -8620,54 +8102,54 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1543-8627 (RESEARCH IN SPORTS MEDICINE (PRINT)); sem registro para 1543-8635. 2021-2024: encontrado por 1543-8627 (RESEARCH IN SPORTS MEDICINE (PRINT)); sem registro para 1543-8635.</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1664-1078 (FRONTIERS IN PSYCHOLOGY). 2021-2024: encontrado por 1664-1078 (FRONTIERS IN PSYCHOLOGY).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>H25</t>
+          <t>O1</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Frontiers in Psychology</t>
+          <t>Biological Rhythm Research</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>1664-1078</t>
+          <t>0929-1016, 1744-4179</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>não classificado na área</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>todas as 29 áreas em que o periódico consta (estrato único); área-mãe: PSICOLOGIA</t>
+          <t>todas as 11 áreas em que o periódico consta (estrato único); área-mãe: ZOOTECNIA / RECURSOS PESQUEIROS</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>não classificado na área</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>todas as 35 áreas em que o periódico consta (estrato único); área-mãe: PSICOLOGIA</t>
+          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: ZOOTECNIA / RECURSOS PESQUEIROS</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -8677,54 +8159,54 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1664-1078 (FRONTIERS IN PSYCHOLOGY). 2021-2024: encontrado por 1664-1078 (FRONTIERS IN PSYCHOLOGY).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 0929-1016, 1744-4179 (BIOLOGICAL RHYTHM RESEARCH; BIOLOGICAL RHYTHM RESEARCH (ONLINE)). 2021-2024: encontrado por 0929-1016, 1744-4179 (BIOLOGICAL RHYTHM RESEARCH; BIOLOGICAL RHYTHM RESEARCH (ONLINE)). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (B2).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>H27</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Biological Rhythm Research</t>
+          <t>Scientific Journal of Sport and Performance</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>0929-1016, 1744-4179</t>
+          <t>2794-0586</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>não classificado na área</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>todas as 11 áreas em que o periódico consta (estrato único); área-mãe: ZOOTECNIA / RECURSOS PESQUEIROS</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>não classificado na área</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: ZOOTECNIA / RECURSOS PESQUEIROS</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -8734,54 +8216,54 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 0929-1016, 1744-4179 (BIOLOGICAL RHYTHM RESEARCH; BIOLOGICAL RHYTHM RESEARCH (ONLINE)). 2021-2024: encontrado por 0929-1016, 1744-4179 (BIOLOGICAL RHYTHM RESEARCH; BIOLOGICAL RHYTHM RESEARCH (ONLINE)). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (B2).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>H27</t>
+          <t>H28</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Scientific Journal of Sport and Performance</t>
+          <t>Children</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2794-0586</t>
+          <t>2227-9067</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>não classificado na área</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>MEDICINA I; MEDICINA II; SAÚDE COLETIVA (área-mãe: SAÚDE COLETIVA)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: MEDICINA II</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -8791,54 +8273,54 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 2227-9067 (CHILDREN). 2021-2024: encontrado por 2227-9067 (CHILDREN). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (A4).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>H28</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Exercise and Quality of Life</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2227-9067</t>
+          <t>2406-1379, 1821-3480</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>não classificado na área</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>MEDICINA I; MEDICINA II; SAÚDE COLETIVA (área-mãe: SAÚDE COLETIVA)</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: MEDICINA II</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -8848,54 +8330,54 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 2227-9067 (CHILDREN). 2021-2024: encontrado por 2227-9067 (CHILDREN). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (A4).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N4</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Exercise and Quality of Life</t>
+          <t>Science &amp; Sports</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2406-1379, 1821-3480</t>
+          <t>0765-1597</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>todas as 9 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -8905,54 +8387,54 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 0765-1597 (SCIENCE &amp; SPORTS). 2021-2024: encontrado por 0765-1597 (SCIENCE &amp; SPORTS).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>N4</t>
+          <t>H29</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Science &amp; Sports</t>
+          <t>Children</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>0765-1597</t>
+          <t>2227-9067</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>não classificado na área</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>todas as 9 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+          <t>MEDICINA I; MEDICINA II; SAÚDE COLETIVA (área-mãe: SAÚDE COLETIVA)</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: MEDICINA II</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -8962,29 +8444,29 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 0765-1597 (SCIENCE &amp; SPORTS). 2021-2024: encontrado por 0765-1597 (SCIENCE &amp; SPORTS).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 2227-9067 (CHILDREN). 2021-2024: encontrado por 2227-9067 (CHILDREN). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (A4).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>H29</t>
+          <t>H30</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Children</t>
+          <t>Retos</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2227-9067</t>
+          <t>1988-2041, 1579-1726</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>não classificado na área</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -8994,22 +8476,22 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>MEDICINA I; MEDICINA II; SAÚDE COLETIVA (área-mãe: SAÚDE COLETIVA)</t>
+          <t>todas as 5 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: MEDICINA II</t>
+          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -9019,54 +8501,54 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 2227-9067 (CHILDREN). 2021-2024: encontrado por 2227-9067 (CHILDREN). 2017-2020: a área 21 não aparece entre as áreas com publicação no quadriênio; pela metodologia 2017-2020 o estrato é único para o periódico (A4).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1988-2041 (RETOS); sem registro para 1579-1726. 2021-2024: encontrado por 1988-2041, 1579-1726 (RETOS: NUEVAS TENDENCIAS EN EDUCACIÓN FÍSICA, DEPORTE Y RECREACIÓN; RETOS).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>H30</t>
+          <t>H31</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Retos</t>
+          <t>Journal of Sport and Health Research</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>1988-2041, 1579-1726</t>
+          <t>1989-6239</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>todas as 5 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+          <t>EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>todas as 19 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
+          <t>EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL; INTERDISCIPLINAR (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -9076,54 +8558,54 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1988-2041 (RETOS); sem registro para 1579-1726. 2021-2024: encontrado por 1988-2041, 1579-1726 (RETOS: NUEVAS TENDENCIAS EN EDUCACIÓN FÍSICA, DEPORTE Y RECREACIÓN; RETOS).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1989-6239 (JOURNAL OF SPORT AND HEALTH RESEARCH). 2021-2024: encontrado por 1989-6239 (JOURNAL OF SPORT AND HEALTH RESEARCH).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>H31</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Journal of Sport and Health Research</t>
+          <t>PLOS ONE</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>1989-6239</t>
+          <t>1932-6203</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
+          <t>todas as 47 áreas em que o periódico consta (estrato único); área-mãe: BIODIVERSIDADE</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL; INTERDISCIPLINAR (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
+          <t>todas as 49 áreas em que o periódico consta (estrato único); área-mãe: BIODIVERSIDADE</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -9133,54 +8615,54 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1989-6239 (JOURNAL OF SPORT AND HEALTH RESEARCH). 2021-2024: encontrado por 1989-6239 (JOURNAL OF SPORT AND HEALTH RESEARCH).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1932-6203 (PLOS ONE). 2021-2024: encontrado por 1932-6203 (PLOS ONE).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N8</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PLOS ONE</t>
+          <t>Scientific Journal of National Pedagogical Dragomanov University. Series 15. Scientific and pedagogical problems of physical culture (physical culture and sports)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>1932-6203</t>
+          <t>2311-2220</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>todas as 47 áreas em que o periódico consta (estrato único); área-mãe: BIODIVERSIDADE</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>não localizado</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>todas as 49 áreas em que o periódico consta (estrato único); área-mãe: BIODIVERSIDADE</t>
+          <t>não localizado na fonte oficial</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -9190,24 +8672,24 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 1932-6203 (PLOS ONE). 2021-2024: encontrado por 1932-6203 (PLOS ONE).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>N8</t>
+          <t>H32</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Scientific Journal of National Pedagogical Dragomanov University. Series 15. Scientific and pedagogical problems of physical culture (physical culture and sports)</t>
+          <t>Acta Kinesiologica</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2311-2220</t>
+          <t>1840-3700, 1840-2976</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -9227,17 +8709,17 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>CIÊNCIAS BIOLÓGICAS II; EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -9247,54 +8729,54 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
+          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: encontrado por 1840-2976 (ACTA KINESIOLOGICA (PRINT)); sem registro para 1840-3700.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>H32</t>
+          <t>H34</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Acta Kinesiologica</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>1840-3700, 1840-2976</t>
+          <t>2075-4663</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>não localizado</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>não localizado na fonte oficial</t>
+          <t>todas as 9 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>CIÊNCIAS BIOLÓGICAS II; EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL (área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL)</t>
+          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -9304,174 +8786,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: encontrado por 1840-2976 (ACTA KINESIOLOGICA (PRINT)); sem registro para 1840-3700.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>H34</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>2075-4663</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>todas as 9 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>todas as 14 áreas em que o periódico consta (estrato único); área-mãe: EDUCAÇÃO FÍSICA, FISIOTERAPIA, FONOAUDIOLOGIA E TERAPIA OCUPACIONAL</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Plataforma Sucupira, consulta pública Qualis Periódicos: https://sucupira-legado.capes.gov.br/sucupira/public/consultas/coleta/veiculoPublicacaoQualis/listaConsultaGeralPeriodicos.jsf</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
           <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: encontrado por 2075-4663 (SPORTS). 2021-2024: encontrado por 2075-4663 (SPORTS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>N6</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Research Square (preprint)</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>não se aplica</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>não consultado (sem periódico/ISSN aplicável)</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>Research Square é servidor de preprints, não periódico; não recebe Qualis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>N9</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Anthropologiai Közlemények</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>2560-0753, 0003-5440</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>não localizado na fonte oficial</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Plataforma Sucupira, consulta pública Qualis Periódicos: https://sucupira-legado.capes.gov.br/sucupira/public/consultas/coleta/veiculoPublicacaoQualis/listaConsultaGeralPeriodicos.jsf</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>ISSN conforme Crossref (base_periodicos.json). 2017-2020: nenhum ISSN consultado consta na consulta (também buscado por título). 2021-2024: nenhum ISSN consultado consta na consulta (também buscado por título).</t>
         </is>
       </c>
     </row>
